--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$130</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5091" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4831" uniqueCount="805">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T08:09:20+00:00</t>
+    <t>2026-01-28T19:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -922,144 +922,6 @@
     <t>MedicationRequest.medication[x].coding</t>
   </si>
   <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.system</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.version</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.code</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.display</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.userSelected</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
     <t>MedicationRequest.medication[x]:medicationCodeableConcept.text</t>
   </si>
   <si>
@@ -1307,16 +1169,112 @@
     <t>MedicationRequest.reasonCode.coding.system</t>
   </si>
   <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
     <t>MedicationRequest.reasonCode.coding.version</t>
   </si>
   <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
     <t>MedicationRequest.reasonCode.coding.code</t>
   </si>
   <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
     <t>MedicationRequest.reasonCode.coding.display</t>
   </si>
   <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
     <t>MedicationRequest.reasonCode.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
   </si>
   <si>
     <t>MedicationRequest.reasonCode.text</t>
@@ -2888,10 +2846,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO137"/>
+  <dimension ref="A1:AO130"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="67.0546875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.75" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="53.40234375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="23.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -6464,19 +6422,23 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>214</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -6524,7 +6486,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6536,7 +6498,7 @@
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>21</v>
@@ -6545,53 +6507,55 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>287</v>
       </c>
       <c r="B32" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="C32" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>135</v>
+        <v>289</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>221</v>
+        <v>264</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>162</v>
+        <v>265</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6629,54 +6593,54 @@
         <v>21</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>223</v>
+        <v>261</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>218</v>
+        <v>272</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6690,7 +6654,7 @@
         <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
@@ -6699,20 +6663,18 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>104</v>
+        <v>292</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -6760,10 +6722,10 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>90</v>
@@ -6775,27 +6737,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>21</v>
+        <v>296</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>21</v>
+        <v>299</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6806,7 +6768,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
@@ -6815,19 +6777,19 @@
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>214</v>
+        <v>302</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6877,7 +6839,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6892,27 +6854,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>21</v>
+        <v>305</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>21</v>
+        <v>307</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6920,10 +6882,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>21</v>
@@ -6932,21 +6894,19 @@
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>110</v>
+        <v>310</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>308</v>
+        <v>258</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>310</v>
-      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
       </c>
@@ -6994,13 +6954,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -7009,27 +6969,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>21</v>
+        <v>312</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>21</v>
+        <v>307</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>313</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7043,7 +7003,7 @@
         <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
@@ -7052,7 +7012,7 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>214</v>
+        <v>315</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>316</v>
@@ -7061,9 +7021,7 @@
         <v>317</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>318</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -7111,7 +7069,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -7126,24 +7084,24 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>21</v>
+        <v>318</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>21</v>
+        <v>319</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>320</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>21</v>
+        <v>321</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>323</v>
@@ -7154,13 +7112,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -7169,20 +7127,16 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>251</v>
+        <v>324</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N37" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="O37" t="s" s="2">
-        <v>327</v>
-      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -7230,7 +7184,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -7245,27 +7199,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>21</v>
+        <v>327</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>330</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7276,7 +7230,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -7285,23 +7239,19 @@
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>214</v>
+        <v>330</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
       </c>
@@ -7349,7 +7299,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>239</v>
+        <v>329</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7364,31 +7314,29 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>21</v>
+        <v>332</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>240</v>
+        <v>333</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>21</v>
+        <v>334</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>21</v>
       </c>
@@ -7397,10 +7345,10 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>21</v>
@@ -7409,16 +7357,16 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>335</v>
+        <v>187</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>264</v>
-      </c>
       <c r="N39" t="s" s="2">
-        <v>265</v>
+        <v>337</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7444,13 +7392,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>21</v>
+        <v>339</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -7468,10 +7416,10 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>261</v>
+        <v>335</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>90</v>
@@ -7483,27 +7431,27 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>270</v>
+        <v>340</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>271</v>
+        <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>272</v>
+        <v>341</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>274</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7511,32 +7459,30 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>339</v>
+        <v>258</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -7585,10 +7531,10 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>90</v>
@@ -7600,22 +7546,22 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>343</v>
+        <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>346</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>347</v>
       </c>
@@ -7631,10 +7577,10 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -7643,10 +7589,10 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>349</v>
@@ -7678,13 +7624,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>21</v>
+        <v>352</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -7708,7 +7654,7 @@
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -7717,27 +7663,27 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>183</v>
+        <v>354</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7748,7 +7694,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -7760,13 +7706,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>356</v>
+        <v>214</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>258</v>
+        <v>215</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>357</v>
+        <v>216</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7817,73 +7763,75 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>355</v>
+        <v>217</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AN42" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>360</v>
-      </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>361</v>
+        <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>362</v>
+        <v>220</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -7920,54 +7868,54 @@
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF43" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AG43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>369</v>
-      </c>
       <c r="B44" t="s" s="2">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7978,10 +7926,10 @@
         <v>90</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -7990,16 +7938,20 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>370</v>
+        <v>225</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>371</v>
+        <v>226</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -8047,13 +7999,13 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>369</v>
+        <v>231</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -8062,27 +8014,27 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>373</v>
+        <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>344</v>
+        <v>232</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>21</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8093,7 +8045,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
@@ -8105,13 +8057,13 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>376</v>
+        <v>214</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>258</v>
+        <v>215</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>377</v>
+        <v>216</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -8162,7 +8114,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>375</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8174,19 +8126,19 @@
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>379</v>
+        <v>218</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>380</v>
+        <v>21</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>21</v>
@@ -8194,21 +8146,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -8217,19 +8169,19 @@
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>258</v>
+        <v>220</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>382</v>
+        <v>221</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>383</v>
+        <v>162</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8255,52 +8207,52 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>384</v>
+        <v>21</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>381</v>
+        <v>223</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>386</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>387</v>
+        <v>218</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -8311,10 +8263,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8322,10 +8274,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -8334,19 +8286,23 @@
         <v>21</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>389</v>
+        <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>258</v>
+        <v>364</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>365</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
       </c>
@@ -8394,7 +8350,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8415,21 +8371,21 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8440,28 +8396,28 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K48" t="s" s="2">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>396</v>
+        <v>374</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8487,13 +8443,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>397</v>
+        <v>21</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -8511,13 +8467,13 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>21</v>
@@ -8526,27 +8482,27 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>399</v>
+        <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>400</v>
+        <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>402</v>
+        <v>21</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>403</v>
+        <v>377</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8554,7 +8510,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>90</v>
@@ -8566,19 +8522,21 @@
         <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>215</v>
+        <v>379</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>216</v>
+        <v>380</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -8626,7 +8584,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>217</v>
+        <v>382</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8638,7 +8596,7 @@
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>21</v>
@@ -8647,32 +8605,32 @@
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>218</v>
+        <v>383</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>21</v>
+        <v>384</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>21</v>
@@ -8681,21 +8639,21 @@
         <v>21</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>220</v>
+        <v>386</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>21</v>
       </c>
@@ -8731,31 +8689,31 @@
         <v>21</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>223</v>
+        <v>389</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>21</v>
@@ -8764,21 +8722,21 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>218</v>
+        <v>390</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>21</v>
+        <v>391</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8786,10 +8744,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -8801,19 +8759,19 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>226</v>
+        <v>393</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>227</v>
+        <v>394</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>228</v>
+        <v>395</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>229</v>
+        <v>396</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -8862,13 +8820,13 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>231</v>
+        <v>397</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
@@ -8883,21 +8841,21 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>232</v>
+        <v>398</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>233</v>
+        <v>399</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8917,19 +8875,23 @@
         <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>214</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -8977,7 +8939,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8989,7 +8951,7 @@
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -8998,25 +8960,25 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>21</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -9026,7 +8988,7 @@
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>21</v>
@@ -9035,16 +8997,16 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>135</v>
+        <v>402</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>220</v>
+        <v>348</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>221</v>
+        <v>403</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>162</v>
+        <v>404</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9082,19 +9044,19 @@
         <v>21</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>223</v>
+        <v>401</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -9106,19 +9068,19 @@
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>21</v>
+        <v>405</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>218</v>
+        <v>406</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>21</v>
@@ -9126,10 +9088,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9137,10 +9099,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -9152,20 +9114,16 @@
         <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>104</v>
+        <v>408</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>291</v>
+        <v>409</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -9213,13 +9171,13 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>295</v>
+        <v>407</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
@@ -9228,27 +9186,27 @@
         <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>296</v>
+        <v>412</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>297</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9259,7 +9217,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -9271,17 +9229,15 @@
         <v>91</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>300</v>
+        <v>414</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -9330,13 +9286,13 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>303</v>
+        <v>413</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
@@ -9351,21 +9307,21 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>304</v>
+        <v>412</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>305</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9388,18 +9344,16 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>110</v>
+        <v>417</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>308</v>
+        <v>418</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>309</v>
+        <v>419</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>310</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -9447,13 +9401,13 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>311</v>
+        <v>416</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
@@ -9462,27 +9416,27 @@
         <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>21</v>
+        <v>420</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>312</v>
+        <v>421</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>313</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9496,7 +9450,7 @@
         <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>21</v>
@@ -9505,17 +9459,17 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>214</v>
+        <v>166</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>316</v>
+        <v>423</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>317</v>
+        <v>424</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>318</v>
+        <v>425</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -9564,7 +9518,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>319</v>
+        <v>422</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9579,27 +9533,27 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>320</v>
+        <v>427</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>321</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9610,7 +9564,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -9619,23 +9573,21 @@
         <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>251</v>
+        <v>187</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>324</v>
+        <v>429</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>325</v>
+        <v>430</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -9659,13 +9611,13 @@
         <v>21</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>21</v>
+        <v>432</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>21</v>
+        <v>433</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>21</v>
@@ -9683,7 +9635,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>328</v>
+        <v>428</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9704,21 +9656,21 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>329</v>
+        <v>434</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>330</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9729,7 +9681,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>21</v>
@@ -9738,23 +9690,19 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>214</v>
+        <v>436</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>238</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -9802,13 +9750,13 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>239</v>
+        <v>435</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>21</v>
@@ -9817,27 +9765,27 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>240</v>
+        <v>439</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9851,7 +9799,7 @@
         <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
@@ -9860,17 +9808,15 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>394</v>
+        <v>442</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -9919,7 +9865,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9934,16 +9880,16 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>183</v>
+        <v>445</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>402</v>
+        <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>21</v>
@@ -9951,10 +9897,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9965,7 +9911,7 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>21</v>
@@ -9974,18 +9920,20 @@
         <v>21</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -10034,7 +9982,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -10049,13 +9997,13 @@
         <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -10066,10 +10014,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10080,7 +10028,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -10089,16 +10037,16 @@
         <v>21</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>104</v>
+        <v>214</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>428</v>
+        <v>215</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>429</v>
+        <v>216</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10149,19 +10097,19 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>427</v>
+        <v>217</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>21</v>
@@ -10170,7 +10118,7 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>426</v>
+        <v>218</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -10181,21 +10129,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>21</v>
@@ -10204,18 +10152,20 @@
         <v>21</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>431</v>
+        <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>432</v>
+        <v>220</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -10252,19 +10202,19 @@
         <v>21</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>430</v>
+        <v>223</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10276,16 +10226,16 @@
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>434</v>
+        <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>435</v>
+        <v>218</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
@@ -10294,45 +10244,47 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>436</v>
+        <v>456</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>21</v>
+        <v>457</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O64" t="s" s="2">
-        <v>439</v>
+        <v>163</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -10381,28 +10333,28 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>440</v>
+        <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>441</v>
+        <v>133</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
@@ -10413,10 +10365,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10427,7 +10379,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -10436,21 +10388,21 @@
         <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>187</v>
+        <v>462</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -10474,13 +10426,13 @@
         <v>21</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>447</v>
+        <v>21</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -10498,7 +10450,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10519,21 +10471,21 @@
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>21</v>
+        <v>468</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10544,7 +10496,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -10553,19 +10505,21 @@
         <v>21</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>450</v>
+        <v>214</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>258</v>
+        <v>470</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>451</v>
+        <v>471</v>
       </c>
       <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+      <c r="O66" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>21</v>
       </c>
@@ -10613,13 +10567,13 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
@@ -10628,27 +10582,27 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>452</v>
+        <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>21</v>
+        <v>474</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10668,19 +10622,23 @@
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>455</v>
+        <v>187</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>477</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -10704,13 +10662,13 @@
         <v>21</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>21</v>
+        <v>480</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>21</v>
+        <v>481</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>21</v>
@@ -10728,7 +10686,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10743,27 +10701,27 @@
         <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>458</v>
+        <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>459</v>
+        <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>21</v>
+        <v>483</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10774,7 +10732,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
@@ -10783,20 +10741,18 @@
         <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>462</v>
+        <v>214</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -10845,13 +10801,13 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>461</v>
+        <v>487</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
@@ -10860,7 +10816,7 @@
         <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>466</v>
+        <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>21</v>
@@ -10872,15 +10828,15 @@
         <v>21</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>21</v>
+        <v>483</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10900,19 +10856,23 @@
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>214</v>
+        <v>489</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>215</v>
+        <v>490</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -10960,7 +10920,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>217</v>
+        <v>494</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10972,7 +10932,7 @@
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
@@ -10981,7 +10941,7 @@
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>218</v>
+        <v>495</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10992,21 +10952,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
@@ -11018,17 +10978,15 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -11065,31 +11023,31 @@
         <v>21</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
@@ -11109,14 +11067,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>471</v>
+        <v>159</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11129,26 +11087,24 @@
         <v>21</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>472</v>
+        <v>220</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>473</v>
+        <v>221</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="O71" t="s" s="2">
-        <v>163</v>
-      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -11184,19 +11140,19 @@
         <v>21</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>474</v>
+        <v>223</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11217,7 +11173,7 @@
         <v>21</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>133</v>
+        <v>218</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
@@ -11228,43 +11184,45 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>21</v>
+        <v>457</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>476</v>
+        <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O72" t="s" s="2">
-        <v>479</v>
+        <v>163</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -11313,19 +11271,19 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>21</v>
@@ -11334,21 +11292,21 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>481</v>
+        <v>133</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>482</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11359,7 +11317,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>21</v>
@@ -11371,17 +11329,17 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>214</v>
+        <v>315</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -11430,13 +11388,13 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
@@ -11451,21 +11409,21 @@
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>481</v>
+        <v>504</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>488</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11476,7 +11434,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>21</v>
@@ -11488,19 +11446,17 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>187</v>
+        <v>506</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -11525,13 +11481,13 @@
         <v>21</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>494</v>
+        <v>21</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>495</v>
+        <v>21</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>21</v>
@@ -11549,19 +11505,19 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>102</v>
+        <v>511</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>21</v>
@@ -11570,21 +11526,21 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>481</v>
+        <v>512</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>497</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11604,16 +11560,16 @@
         <v>21</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
         <v>214</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>499</v>
+        <v>215</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>500</v>
+        <v>216</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11664,7 +11620,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>501</v>
+        <v>217</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11676,7 +11632,7 @@
         <v>21</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>21</v>
@@ -11685,32 +11641,32 @@
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>481</v>
+        <v>218</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>497</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>21</v>
@@ -11719,23 +11675,21 @@
         <v>21</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>503</v>
+        <v>135</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>504</v>
+        <v>220</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>505</v>
+        <v>221</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>21</v>
       </c>
@@ -11771,31 +11725,31 @@
         <v>21</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>508</v>
+        <v>223</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>21</v>
@@ -11804,7 +11758,7 @@
         <v>21</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>509</v>
+        <v>218</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>21</v>
@@ -11815,10 +11769,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11838,16 +11792,16 @@
         <v>21</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>214</v>
+        <v>516</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>215</v>
+        <v>517</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>216</v>
+        <v>518</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11898,7 +11852,7 @@
         <v>21</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>217</v>
+        <v>519</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11910,7 +11864,7 @@
         <v>21</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>21</v>
@@ -11919,7 +11873,7 @@
         <v>21</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>218</v>
+        <v>520</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>21</v>
@@ -11930,21 +11884,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>21</v>
@@ -11953,21 +11907,23 @@
         <v>21</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>135</v>
+        <v>522</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>220</v>
+        <v>523</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>221</v>
+        <v>524</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>21</v>
       </c>
@@ -12003,31 +11959,31 @@
         <v>21</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>223</v>
+        <v>527</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>21</v>
@@ -12036,7 +11992,7 @@
         <v>21</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>218</v>
+        <v>528</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>21</v>
@@ -12047,46 +12003,42 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>471</v>
+        <v>21</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J79" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>135</v>
+        <v>522</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>472</v>
+        <v>530</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>21</v>
       </c>
@@ -12134,19 +12086,19 @@
         <v>21</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>474</v>
+        <v>532</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>21</v>
@@ -12155,7 +12107,7 @@
         <v>21</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>133</v>
+        <v>528</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>21</v>
@@ -12166,10 +12118,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12180,7 +12132,7 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>21</v>
@@ -12192,17 +12144,19 @@
         <v>91</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>361</v>
+        <v>534</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="O80" t="s" s="2">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>21</v>
@@ -12251,13 +12205,13 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>517</v>
+        <v>539</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>21</v>
@@ -12272,7 +12226,7 @@
         <v>21</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>518</v>
+        <v>540</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>21</v>
@@ -12283,10 +12237,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>519</v>
+        <v>541</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12309,17 +12263,19 @@
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>521</v>
+        <v>542</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="O81" t="s" s="2">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>21</v>
@@ -12368,7 +12324,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12380,7 +12336,7 @@
         <v>21</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>525</v>
+        <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>21</v>
@@ -12389,7 +12345,7 @@
         <v>21</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>21</v>
@@ -12400,10 +12356,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12423,16 +12379,16 @@
         <v>21</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>215</v>
+        <v>546</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>216</v>
+        <v>547</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12459,13 +12415,13 @@
         <v>21</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>21</v>
+        <v>548</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>21</v>
+        <v>549</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>21</v>
@@ -12483,7 +12439,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>217</v>
+        <v>550</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12495,7 +12451,7 @@
         <v>21</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>21</v>
@@ -12504,7 +12460,7 @@
         <v>21</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>218</v>
+        <v>551</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>21</v>
@@ -12515,21 +12471,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>21</v>
@@ -12538,25 +12494,25 @@
         <v>21</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>135</v>
+        <v>522</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>220</v>
+        <v>553</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q83" s="2"/>
+      <c r="Q83" t="s" s="2">
+        <v>555</v>
+      </c>
       <c r="R83" t="s" s="2">
         <v>21</v>
       </c>
@@ -12588,31 +12544,31 @@
         <v>21</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>223</v>
+        <v>556</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>21</v>
@@ -12621,7 +12577,7 @@
         <v>21</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>218</v>
+        <v>540</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>21</v>
@@ -12632,10 +12588,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>529</v>
+        <v>557</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>529</v>
+        <v>557</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12658,13 +12614,13 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>531</v>
+        <v>558</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>532</v>
+        <v>559</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12715,7 +12671,7 @@
         <v>21</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>533</v>
+        <v>560</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12736,7 +12692,7 @@
         <v>21</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>21</v>
@@ -12747,10 +12703,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>535</v>
+        <v>561</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>535</v>
+        <v>561</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12773,20 +12729,16 @@
         <v>91</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>537</v>
+        <v>562</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>540</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>21</v>
       </c>
@@ -12834,7 +12786,7 @@
         <v>21</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>541</v>
+        <v>564</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12855,7 +12807,7 @@
         <v>21</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>21</v>
@@ -12866,10 +12818,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>543</v>
+        <v>565</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>543</v>
+        <v>565</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12892,13 +12844,13 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>544</v>
+        <v>566</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>545</v>
+        <v>567</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12949,7 +12901,7 @@
         <v>21</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>546</v>
+        <v>568</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12970,7 +12922,7 @@
         <v>21</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>21</v>
@@ -12981,10 +12933,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>547</v>
+        <v>569</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>547</v>
+        <v>569</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13007,20 +12959,16 @@
         <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>548</v>
+        <v>110</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>21</v>
       </c>
@@ -13044,13 +12992,13 @@
         <v>21</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>21</v>
+        <v>548</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>21</v>
+        <v>549</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>21</v>
@@ -13068,7 +13016,7 @@
         <v>21</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13089,7 +13037,7 @@
         <v>21</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>21</v>
@@ -13100,10 +13048,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>555</v>
+        <v>573</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>555</v>
+        <v>573</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13114,7 +13062,7 @@
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>21</v>
@@ -13126,20 +13074,18 @@
         <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>548</v>
+        <v>110</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>556</v>
+        <v>574</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>557</v>
+        <v>575</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>21</v>
       </c>
@@ -13163,13 +13109,11 @@
         <v>21</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>21</v>
+        <v>577</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>21</v>
@@ -13187,13 +13131,13 @@
         <v>21</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>558</v>
+        <v>578</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>21</v>
@@ -13208,7 +13152,7 @@
         <v>21</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>554</v>
+        <v>218</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>21</v>
@@ -13219,10 +13163,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13233,7 +13177,7 @@
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>21</v>
@@ -13245,15 +13189,17 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>560</v>
+        <v>581</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>583</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>21</v>
@@ -13278,13 +13224,13 @@
         <v>21</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>562</v>
+        <v>21</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>563</v>
+        <v>21</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>21</v>
@@ -13302,13 +13248,13 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>21</v>
@@ -13323,7 +13269,7 @@
         <v>21</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>565</v>
+        <v>218</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>21</v>
@@ -13334,10 +13280,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13348,7 +13294,7 @@
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>21</v>
@@ -13360,22 +13306,24 @@
         <v>91</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>536</v>
+        <v>110</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>567</v>
+        <v>586</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q90" t="s" s="2">
-        <v>569</v>
-      </c>
+      <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
         <v>21</v>
       </c>
@@ -13395,13 +13343,11 @@
         <v>21</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>21</v>
+        <v>590</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>21</v>
@@ -13419,13 +13365,13 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>21</v>
@@ -13440,7 +13386,7 @@
         <v>21</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>554</v>
+        <v>592</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>21</v>
@@ -13451,10 +13397,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>571</v>
+        <v>593</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>571</v>
+        <v>593</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13477,13 +13423,13 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>536</v>
+        <v>594</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>572</v>
+        <v>595</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>573</v>
+        <v>596</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13534,7 +13480,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>574</v>
+        <v>597</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13555,7 +13501,7 @@
         <v>21</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>554</v>
+        <v>598</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>21</v>
@@ -13566,10 +13512,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13592,15 +13538,17 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>548</v>
+        <v>187</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>576</v>
+        <v>600</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>601</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>602</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>21</v>
@@ -13625,13 +13573,13 @@
         <v>21</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>21</v>
+        <v>603</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>21</v>
+        <v>604</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>21</v>
@@ -13649,7 +13597,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>578</v>
+        <v>605</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13670,7 +13618,7 @@
         <v>21</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>554</v>
+        <v>606</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>21</v>
@@ -13681,10 +13629,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>579</v>
+        <v>607</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>579</v>
+        <v>607</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13707,15 +13655,17 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>548</v>
+        <v>608</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>580</v>
+        <v>609</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>610</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>611</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>21</v>
@@ -13740,13 +13690,13 @@
         <v>21</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>21</v>
+        <v>612</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>21</v>
+        <v>613</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>21</v>
@@ -13764,7 +13714,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>582</v>
+        <v>614</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13785,21 +13735,21 @@
         <v>21</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>554</v>
+        <v>615</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>21</v>
+        <v>616</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>583</v>
+        <v>617</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>583</v>
+        <v>617</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13822,16 +13772,20 @@
         <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>584</v>
+        <v>618</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>619</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>621</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>21</v>
       </c>
@@ -13855,13 +13809,13 @@
         <v>21</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>562</v>
+        <v>622</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>563</v>
+        <v>623</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>21</v>
@@ -13879,7 +13833,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>586</v>
+        <v>624</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13900,21 +13854,21 @@
         <v>21</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>565</v>
+        <v>625</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>21</v>
+        <v>626</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>587</v>
+        <v>627</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>587</v>
+        <v>627</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13925,7 +13879,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>21</v>
@@ -13937,18 +13891,18 @@
         <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>588</v>
+        <v>628</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>629</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>630</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>21</v>
       </c>
@@ -13972,11 +13926,13 @@
         <v>21</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y95" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="Z95" t="s" s="2">
-        <v>591</v>
+        <v>632</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>21</v>
@@ -13994,13 +13950,13 @@
         <v>21</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>592</v>
+        <v>633</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>21</v>
@@ -14015,21 +13971,21 @@
         <v>21</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>218</v>
+        <v>634</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>21</v>
+        <v>635</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>593</v>
+        <v>636</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>593</v>
+        <v>636</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14040,7 +13996,7 @@
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>21</v>
@@ -14052,18 +14008,20 @@
         <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>594</v>
+        <v>187</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>595</v>
+        <v>637</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>596</v>
+        <v>638</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>639</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>640</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>21</v>
       </c>
@@ -14087,13 +14045,13 @@
         <v>21</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>21</v>
+        <v>641</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>21</v>
+        <v>642</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>21</v>
@@ -14111,13 +14069,13 @@
         <v>21</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>598</v>
+        <v>643</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>21</v>
@@ -14132,21 +14090,21 @@
         <v>21</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>218</v>
+        <v>644</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>21</v>
+        <v>645</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>599</v>
+        <v>646</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>599</v>
+        <v>646</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14169,20 +14127,16 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>110</v>
+        <v>506</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>600</v>
+        <v>647</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>603</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>21</v>
       </c>
@@ -14206,11 +14160,13 @@
         <v>21</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y97" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z97" t="s" s="2">
-        <v>604</v>
+        <v>21</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>21</v>
@@ -14228,7 +14184,7 @@
         <v>21</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>605</v>
+        <v>649</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14249,21 +14205,21 @@
         <v>21</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>606</v>
+        <v>21</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>21</v>
+        <v>650</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>607</v>
+        <v>651</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>607</v>
+        <v>651</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14283,16 +14239,16 @@
         <v>21</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>608</v>
+        <v>214</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>609</v>
+        <v>215</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>610</v>
+        <v>216</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14343,7 +14299,7 @@
         <v>21</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>611</v>
+        <v>217</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14355,7 +14311,7 @@
         <v>21</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>21</v>
@@ -14364,7 +14320,7 @@
         <v>21</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>612</v>
+        <v>218</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>21</v>
@@ -14375,21 +14331,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>613</v>
+        <v>652</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>613</v>
+        <v>652</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>21</v>
@@ -14398,19 +14354,19 @@
         <v>21</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>614</v>
+        <v>220</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>615</v>
+        <v>221</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>616</v>
+        <v>162</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14436,43 +14392,43 @@
         <v>21</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>617</v>
+        <v>21</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>618</v>
+        <v>21</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>619</v>
+        <v>223</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>21</v>
@@ -14481,7 +14437,7 @@
         <v>21</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>620</v>
+        <v>218</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>21</v>
@@ -14492,10 +14448,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>621</v>
+        <v>653</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>621</v>
+        <v>653</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14518,18 +14474,18 @@
         <v>91</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>622</v>
+        <v>187</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>623</v>
+        <v>654</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="O100" s="2"/>
+        <v>655</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>656</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>21</v>
       </c>
@@ -14556,10 +14512,10 @@
         <v>191</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>626</v>
+        <v>657</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>627</v>
+        <v>658</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>21</v>
@@ -14577,7 +14533,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>628</v>
+        <v>659</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14598,21 +14554,21 @@
         <v>21</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>629</v>
+        <v>21</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>630</v>
+        <v>660</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14635,19 +14591,19 @@
         <v>91</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>187</v>
+        <v>662</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>632</v>
+        <v>663</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>633</v>
+        <v>664</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>634</v>
+        <v>665</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>635</v>
+        <v>666</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>21</v>
@@ -14672,13 +14628,13 @@
         <v>21</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>636</v>
+        <v>21</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>637</v>
+        <v>21</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>21</v>
@@ -14696,7 +14652,7 @@
         <v>21</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>638</v>
+        <v>667</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14717,21 +14673,21 @@
         <v>21</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>640</v>
+        <v>668</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>641</v>
+        <v>669</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>641</v>
+        <v>669</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14742,7 +14698,7 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>21</v>
@@ -14754,17 +14710,19 @@
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>187</v>
+        <v>670</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>642</v>
+        <v>671</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>673</v>
+      </c>
       <c r="O102" t="s" s="2">
-        <v>644</v>
+        <v>674</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>21</v>
@@ -14789,13 +14747,13 @@
         <v>21</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>645</v>
+        <v>21</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>646</v>
+        <v>21</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>21</v>
@@ -14813,7 +14771,7 @@
         <v>21</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>647</v>
+        <v>675</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14834,21 +14792,21 @@
         <v>21</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>648</v>
+        <v>676</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>649</v>
+        <v>677</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>650</v>
+        <v>678</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>650</v>
+        <v>678</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14871,19 +14829,19 @@
         <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>187</v>
+        <v>679</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>651</v>
+        <v>680</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>652</v>
+        <v>681</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>653</v>
+        <v>682</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>654</v>
+        <v>683</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>21</v>
@@ -14908,13 +14866,13 @@
         <v>21</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>655</v>
+        <v>21</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>656</v>
+        <v>21</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>21</v>
@@ -14932,7 +14890,7 @@
         <v>21</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>657</v>
+        <v>684</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14953,21 +14911,21 @@
         <v>21</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>658</v>
+        <v>685</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>659</v>
+        <v>686</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>660</v>
+        <v>687</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>660</v>
+        <v>687</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14978,7 +14936,7 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>21</v>
@@ -14990,16 +14948,20 @@
         <v>91</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>520</v>
+        <v>688</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>661</v>
+        <v>689</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+        <v>690</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>692</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>21</v>
       </c>
@@ -15047,13 +15009,13 @@
         <v>21</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>663</v>
+        <v>693</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>21</v>
@@ -15068,21 +15030,21 @@
         <v>21</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>21</v>
+        <v>694</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>664</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>665</v>
+        <v>695</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>665</v>
+        <v>695</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15102,19 +15064,21 @@
         <v>21</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>214</v>
+        <v>688</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>215</v>
+        <v>696</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>216</v>
+        <v>697</v>
       </c>
       <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+      <c r="O105" t="s" s="2">
+        <v>698</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>21</v>
       </c>
@@ -15162,7 +15126,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>217</v>
+        <v>699</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15174,7 +15138,7 @@
         <v>21</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>21</v>
@@ -15183,7 +15147,7 @@
         <v>21</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>218</v>
+        <v>694</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>21</v>
@@ -15194,21 +15158,21 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>666</v>
+        <v>700</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>666</v>
+        <v>700</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>21</v>
@@ -15220,17 +15184,15 @@
         <v>21</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>135</v>
+        <v>701</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>220</v>
+        <v>702</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>21</v>
@@ -15267,40 +15229,40 @@
         <v>21</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>223</v>
+        <v>700</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>21</v>
+        <v>704</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>218</v>
+        <v>705</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>21</v>
@@ -15311,10 +15273,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>667</v>
+        <v>706</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>667</v>
+        <v>706</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15334,21 +15296,19 @@
         <v>21</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>668</v>
+        <v>215</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>669</v>
+        <v>216</v>
       </c>
       <c r="N107" s="2"/>
-      <c r="O107" t="s" s="2">
-        <v>670</v>
-      </c>
+      <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>21</v>
       </c>
@@ -15372,13 +15332,13 @@
         <v>21</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>671</v>
+        <v>21</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>672</v>
+        <v>21</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>21</v>
@@ -15396,7 +15356,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>673</v>
+        <v>217</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15408,7 +15368,7 @@
         <v>21</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>21</v>
@@ -15417,32 +15377,32 @@
         <v>21</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>674</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>675</v>
+        <v>707</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>675</v>
+        <v>707</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>21</v>
@@ -15451,23 +15411,21 @@
         <v>21</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>676</v>
+        <v>135</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>677</v>
+        <v>220</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>678</v>
+        <v>221</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>680</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>21</v>
       </c>
@@ -15515,19 +15473,19 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>681</v>
+        <v>223</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>21</v>
@@ -15536,56 +15494,56 @@
         <v>21</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>658</v>
+        <v>218</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>682</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>683</v>
+        <v>708</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>683</v>
+        <v>708</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>21</v>
+        <v>457</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J109" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>684</v>
+        <v>135</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>685</v>
+        <v>458</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>686</v>
+        <v>459</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>687</v>
+        <v>162</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>688</v>
+        <v>163</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>21</v>
@@ -15634,19 +15592,19 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>689</v>
+        <v>460</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>21</v>
@@ -15655,21 +15613,21 @@
         <v>21</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>690</v>
+        <v>133</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>691</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>692</v>
+        <v>709</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>692</v>
+        <v>709</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15689,23 +15647,21 @@
         <v>21</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>694</v>
+        <v>710</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>695</v>
+        <v>711</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>697</v>
-      </c>
+        <v>712</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>21</v>
       </c>
@@ -15753,7 +15709,7 @@
         <v>21</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15774,21 +15730,21 @@
         <v>21</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>699</v>
+        <v>713</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>700</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15808,23 +15764,19 @@
         <v>21</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>702</v>
+        <v>214</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>703</v>
+        <v>215</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>706</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>21</v>
       </c>
@@ -15872,7 +15824,7 @@
         <v>21</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>707</v>
+        <v>217</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15884,7 +15836,7 @@
         <v>21</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>21</v>
@@ -15893,7 +15845,7 @@
         <v>21</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>708</v>
+        <v>218</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>21</v>
@@ -15904,21 +15856,21 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>21</v>
@@ -15927,21 +15879,21 @@
         <v>21</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>702</v>
+        <v>135</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>710</v>
+        <v>220</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" t="s" s="2">
-        <v>712</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>21</v>
       </c>
@@ -15989,19 +15941,19 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>713</v>
+        <v>223</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>21</v>
@@ -16010,7 +15962,7 @@
         <v>21</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>708</v>
+        <v>218</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>21</v>
@@ -16021,42 +15973,46 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>21</v>
+        <v>457</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>715</v>
+        <v>135</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>716</v>
+        <v>458</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>21</v>
       </c>
@@ -16104,28 +16060,28 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>714</v>
+        <v>460</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>718</v>
+        <v>21</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>719</v>
+        <v>133</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>21</v>
@@ -16136,10 +16092,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16162,13 +16118,13 @@
         <v>21</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>214</v>
+        <v>688</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>215</v>
+        <v>718</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>216</v>
+        <v>719</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -16219,7 +16175,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>217</v>
+        <v>717</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16231,7 +16187,7 @@
         <v>21</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>21</v>
@@ -16240,7 +16196,7 @@
         <v>21</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>218</v>
+        <v>720</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>21</v>
@@ -16258,14 +16214,14 @@
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>21</v>
@@ -16277,17 +16233,15 @@
         <v>21</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>135</v>
+        <v>722</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>220</v>
+        <v>723</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>724</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>21</v>
@@ -16336,19 +16290,19 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>223</v>
+        <v>721</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>21</v>
@@ -16357,7 +16311,7 @@
         <v>21</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>218</v>
+        <v>725</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>21</v>
@@ -16368,46 +16322,42 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>471</v>
+        <v>21</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>135</v>
+        <v>722</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>472</v>
+        <v>727</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>728</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>21</v>
       </c>
@@ -16455,19 +16405,19 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>474</v>
+        <v>726</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>21</v>
@@ -16476,7 +16426,7 @@
         <v>21</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>133</v>
+        <v>725</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>21</v>
@@ -16487,10 +16437,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16513,18 +16463,20 @@
         <v>21</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>715</v>
+        <v>730</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>733</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>734</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>21</v>
       </c>
@@ -16572,7 +16524,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16590,10 +16542,10 @@
         <v>21</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>21</v>
+        <v>735</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>727</v>
+        <v>736</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>21</v>
@@ -16604,10 +16556,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>728</v>
+        <v>737</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16630,15 +16582,17 @@
         <v>21</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>214</v>
+        <v>594</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>215</v>
+        <v>738</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>739</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>740</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>21</v>
@@ -16687,7 +16641,7 @@
         <v>21</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>217</v>
+        <v>737</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16699,41 +16653,41 @@
         <v>21</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>21</v>
+        <v>741</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>218</v>
+        <v>742</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>21</v>
+        <v>743</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>21</v>
@@ -16745,17 +16699,15 @@
         <v>21</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>135</v>
+        <v>688</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>220</v>
+        <v>745</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>746</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>21</v>
@@ -16804,78 +16756,76 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>223</v>
+        <v>744</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>21</v>
+        <v>747</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>218</v>
+        <v>748</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>21</v>
+        <v>749</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>730</v>
+        <v>750</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>730</v>
+        <v>750</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>471</v>
+        <v>21</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>135</v>
+        <v>722</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>472</v>
+        <v>751</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>473</v>
+        <v>752</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>753</v>
+      </c>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>21</v>
       </c>
@@ -16923,28 +16873,28 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>474</v>
+        <v>750</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>21</v>
+        <v>754</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>133</v>
+        <v>755</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>21</v>
@@ -16955,10 +16905,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>731</v>
+        <v>756</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>731</v>
+        <v>756</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16981,13 +16931,13 @@
         <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>702</v>
+        <v>757</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>732</v>
+        <v>758</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>733</v>
+        <v>759</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -17038,7 +16988,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>731</v>
+        <v>756</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17059,10 +17009,10 @@
         <v>21</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>734</v>
+        <v>760</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>21</v>
+        <v>346</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>21</v>
@@ -17070,10 +17020,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>735</v>
+        <v>761</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>735</v>
+        <v>761</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17096,13 +17046,13 @@
         <v>21</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>736</v>
+        <v>701</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>737</v>
+        <v>762</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>738</v>
+        <v>763</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -17153,7 +17103,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>735</v>
+        <v>761</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17171,10 +17121,10 @@
         <v>21</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>21</v>
+        <v>764</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>739</v>
+        <v>765</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>21</v>
@@ -17185,10 +17135,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>740</v>
+        <v>766</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>740</v>
+        <v>766</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17211,13 +17161,13 @@
         <v>21</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>736</v>
+        <v>214</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>741</v>
+        <v>215</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>742</v>
+        <v>216</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -17268,7 +17218,7 @@
         <v>21</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>740</v>
+        <v>217</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17280,7 +17230,7 @@
         <v>21</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>21</v>
@@ -17289,7 +17239,7 @@
         <v>21</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>739</v>
+        <v>218</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>21</v>
@@ -17300,21 +17250,21 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>743</v>
+        <v>767</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>743</v>
+        <v>767</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>21</v>
@@ -17326,20 +17276,18 @@
         <v>21</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>744</v>
+        <v>135</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>745</v>
+        <v>220</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>746</v>
+        <v>221</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>748</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>21</v>
       </c>
@@ -17387,28 +17335,28 @@
         <v>21</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>743</v>
+        <v>223</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>749</v>
+        <v>21</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>750</v>
+        <v>218</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>21</v>
@@ -17419,44 +17367,46 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>751</v>
+        <v>768</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>751</v>
+        <v>768</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>21</v>
+        <v>457</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>608</v>
+        <v>135</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>752</v>
+        <v>458</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>753</v>
+        <v>459</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="O125" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>21</v>
       </c>
@@ -17504,42 +17454,42 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>751</v>
+        <v>460</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>755</v>
+        <v>21</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>756</v>
+        <v>133</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>757</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>758</v>
+        <v>769</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>758</v>
+        <v>769</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17547,7 +17497,7 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>90</v>
@@ -17562,15 +17512,17 @@
         <v>21</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>702</v>
+        <v>608</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>759</v>
+        <v>770</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="N126" s="2"/>
+        <v>771</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>772</v>
+      </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>21</v>
@@ -17595,13 +17547,13 @@
         <v>21</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>21</v>
+        <v>773</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>21</v>
+        <v>774</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>21</v>
@@ -17619,10 +17571,10 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>758</v>
+        <v>769</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>90</v>
@@ -17637,24 +17589,24 @@
         <v>21</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>762</v>
+        <v>775</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>763</v>
+        <v>776</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>764</v>
+        <v>777</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>764</v>
+        <v>777</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17677,17 +17629,15 @@
         <v>21</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>736</v>
+        <v>187</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>765</v>
+        <v>778</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>767</v>
-      </c>
+        <v>779</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>21</v>
@@ -17712,13 +17662,13 @@
         <v>21</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>21</v>
+        <v>780</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>21</v>
+        <v>781</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>21</v>
@@ -17736,7 +17686,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>764</v>
+        <v>777</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17754,24 +17704,24 @@
         <v>21</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>768</v>
+        <v>782</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>769</v>
+        <v>783</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>21</v>
+        <v>784</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17794,13 +17744,13 @@
         <v>21</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>771</v>
+        <v>786</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>773</v>
+        <v>788</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17851,7 +17801,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17866,16 +17816,16 @@
         <v>102</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>21</v>
+        <v>789</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>21</v>
+        <v>782</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>774</v>
+        <v>790</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>21</v>
@@ -17883,21 +17833,21 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>775</v>
+        <v>791</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>775</v>
+        <v>791</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>21</v>
+        <v>792</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>21</v>
@@ -17909,15 +17859,17 @@
         <v>21</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>715</v>
+        <v>793</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>776</v>
+        <v>794</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="N129" s="2"/>
+        <v>795</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>796</v>
+      </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>21</v>
@@ -17966,13 +17918,13 @@
         <v>21</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>775</v>
+        <v>791</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>21</v>
@@ -17984,10 +17936,10 @@
         <v>21</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>778</v>
+        <v>21</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>21</v>
@@ -17998,10 +17950,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>780</v>
+        <v>798</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>780</v>
+        <v>798</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18012,7 +17964,7 @@
         <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>21</v>
@@ -18024,15 +17976,17 @@
         <v>21</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>214</v>
+        <v>799</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>215</v>
+        <v>800</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N130" s="2"/>
+        <v>801</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>802</v>
+      </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>21</v>
@@ -18081,855 +18035,38 @@
         <v>21</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>217</v>
+        <v>798</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>21</v>
+        <v>803</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>218</v>
+        <v>804</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="131" hidden="true">
-      <c r="A131" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O131" s="2"/>
-      <c r="P131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="132" hidden="true">
-      <c r="A132" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="P132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="133" hidden="true">
-      <c r="A133" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="O133" s="2"/>
-      <c r="P133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="134" hidden="true">
-      <c r="A134" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="N134" s="2"/>
-      <c r="O134" s="2"/>
-      <c r="P134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>796</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="135" hidden="true">
-      <c r="A135" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>801</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
-      <c r="P135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>803</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>796</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="136" hidden="true">
-      <c r="A136" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="E136" s="2"/>
-      <c r="F136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>808</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="O136" s="2"/>
-      <c r="P136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="137" hidden="true">
-      <c r="A137" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="O137" s="2"/>
-      <c r="P137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO137" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO137">
+  <autoFilter ref="A1:AO130">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18939,7 +18076,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI136">
+  <conditionalFormatting sqref="A2:AI129">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T19:29:09+00:00</t>
+    <t>2026-01-29T08:16:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>ELGA e-Medikation Geplante Abgabe</t>
+    <t>ELGA e-Med Geplante Abgabe</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T08:16:48+00:00</t>
+    <t>2026-01-29T15:27:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet eine geplante Abgabe eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab.
+    <t>**Beschreibung:** Bildet eine geplante Abgabe eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
 Sie enthält das verordnete Arzneimittel und dessen Dosierung und spielgelt die Inhalte des e-Rezepts wider. Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation.
 Als groupIdentifier dient die Geplante-Abgabe-ID (früher eMED-ID), die auch im e-Rezept mitgeführt wird.
 Werden mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer'). Verwendet R5 Backport Extensions.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2797" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2797" uniqueCount="524">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T14:55:57+00:00</t>
+    <t>2026-02-09T17:27:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1646,6 +1646,9 @@
   <si>
     <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
+  </si>
+  <si>
+    <t>Referenenz auf DetectedIssue Ressource. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates an actual or potential clinical issue with or between one or more active or proposed clinical actions for a patient; e.g. Drug-drug interaction, duplicate therapy, dosage alert etc.</t>
@@ -10585,13 +10588,13 @@
         <v>512</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>231</v>
+        <v>513</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10662,7 +10665,7 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10673,10 +10676,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10699,16 +10702,16 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10758,7 +10761,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10773,13 +10776,13 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AL75" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T17:27:03+00:00</t>
+    <t>2026-02-10T17:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T17:53:58+00:00</t>
+    <t>2026-02-12T16:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}med-1:Für die geplante Abgabe muss entweder CodeableConcept (PZN) oder Reference(Medication) angegeben werden – aber genau eins. {medicationCodeableConcept.exists() xor medicationReference.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T16:23:56+00:00</t>
+    <t>2026-02-16T10:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2797" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2796" uniqueCount="523">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T10:10:16+00:00</t>
+    <t>2026-02-16T15:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -572,7 +572,8 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status der geplanten Abgabe (im Standardfall active oder complete): active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown -&gt; entfernen: draft, unknown</t>
+    <t>Status der geplanten Abgabe (im Standardfall active oder complete): 
+ (req) active | on-hold | cancelled | completed | entered-in-error | stopped  (entfernt: draft | unknown); TODO: Fachlich zu prüfen.</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -584,10 +585,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>A coded concept specifying the state of the prescribing event. Describes the lifecycle of the prescription.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/GeplanteAbgabeStatusVS</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -3690,7 +3688,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>175</v>
       </c>
@@ -3709,7 +3707,7 @@
         <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>91</v>
@@ -3755,11 +3753,9 @@
       <c r="X15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Y15" s="2"/>
+      <c r="Z15" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3792,16 +3788,16 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>21</v>
@@ -3809,10 +3805,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3835,16 +3831,16 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>190</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3870,14 +3866,14 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>193</v>
-      </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
       </c>
@@ -3894,7 +3890,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3909,13 +3905,13 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>21</v>
@@ -3926,10 +3922,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3955,13 +3951,13 @@
         <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3972,7 +3968,7 @@
         <v>21</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>21</v>
@@ -3990,11 +3986,11 @@
         <v>179</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>202</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
       </c>
@@ -4011,7 +4007,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -4026,16 +4022,16 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>21</v>
@@ -4043,10 +4039,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4069,16 +4065,16 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4089,29 +4085,29 @@
         <v>21</v>
       </c>
       <c r="S18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Y18" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="T18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="Y18" t="s" s="2">
+      <c r="Z18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z18" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
       </c>
@@ -4128,7 +4124,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4146,13 +4142,13 @@
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AM18" t="s" s="2">
-        <v>214</v>
-      </c>
       <c r="AN18" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>21</v>
@@ -4160,10 +4156,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4189,10 +4185,10 @@
         <v>110</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4222,11 +4218,11 @@
         <v>179</v>
       </c>
       <c r="Y19" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="Z19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="Z19" t="s" s="2">
-        <v>219</v>
-      </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
       </c>
@@ -4243,7 +4239,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4258,16 +4254,16 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>21</v>
@@ -4275,10 +4271,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4301,16 +4297,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4360,7 +4356,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4381,7 +4377,7 @@
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>21</v>
@@ -4392,10 +4388,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4418,13 +4414,13 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4475,7 +4471,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4496,7 +4492,7 @@
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>21</v>
@@ -4507,10 +4503,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4533,16 +4529,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4568,29 +4564,29 @@
         <v>21</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Y22" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="Z22" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="Z22" t="s" s="2">
+      <c r="AA22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB22" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>90</v>
@@ -4605,30 +4601,30 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>247</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>21</v>
@@ -4650,16 +4646,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4689,7 +4685,7 @@
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4707,7 +4703,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>90</v>
@@ -4722,27 +4718,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>247</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4765,13 +4761,13 @@
         <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4822,7 +4818,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4843,7 +4839,7 @@
         <v>21</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>21</v>
@@ -4854,10 +4850,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4883,10 +4879,10 @@
         <v>135</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>162</v>
@@ -4930,7 +4926,7 @@
         <v>138</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>21</v>
@@ -4939,7 +4935,7 @@
         <v>139</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4960,7 +4956,7 @@
         <v>21</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>21</v>
@@ -4971,10 +4967,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4997,19 +4993,19 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -5058,7 +5054,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5079,21 +5075,21 @@
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5116,19 +5112,19 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -5177,7 +5173,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5198,24 +5194,24 @@
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="C28" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>21</v>
@@ -5237,16 +5233,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>287</v>
-      </c>
       <c r="M28" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5296,7 +5292,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>90</v>
@@ -5311,27 +5307,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>247</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5354,16 +5350,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5413,7 +5409,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>90</v>
@@ -5428,27 +5424,27 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>297</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5471,16 +5467,16 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="L30" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5530,7 +5526,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5545,27 +5541,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5588,13 +5584,13 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5645,7 +5641,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5660,16 +5656,16 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="AN31" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>21</v>
@@ -5677,10 +5673,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5703,13 +5699,13 @@
         <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5760,7 +5756,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5775,27 +5771,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5818,13 +5814,13 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5875,7 +5871,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5890,16 +5886,16 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
@@ -5907,10 +5903,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5933,13 +5929,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5990,7 +5986,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6005,16 +6001,16 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>21</v>
@@ -6022,10 +6018,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6048,16 +6044,16 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M35" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6083,14 +6079,14 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>336</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
       </c>
@@ -6107,7 +6103,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6122,13 +6118,13 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
@@ -6139,10 +6135,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6165,13 +6161,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6222,7 +6218,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6243,10 +6239,10 @@
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
@@ -6254,10 +6250,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6280,16 +6276,16 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6315,14 +6311,14 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
       </c>
@@ -6339,7 +6335,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6354,27 +6350,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>354</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6397,13 +6393,13 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6454,7 +6450,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6475,7 +6471,7 @@
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6486,10 +6482,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6515,10 +6511,10 @@
         <v>135</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>162</v>
@@ -6562,7 +6558,7 @@
         <v>138</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>21</v>
@@ -6571,7 +6567,7 @@
         <v>139</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6592,7 +6588,7 @@
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6603,10 +6599,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6629,19 +6625,19 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6690,7 +6686,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6711,21 +6707,21 @@
         <v>21</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>274</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6748,19 +6744,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6809,7 +6805,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6830,21 +6826,21 @@
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6867,16 +6863,16 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L42" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6926,7 +6922,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6941,16 +6937,16 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AL42" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>364</v>
-      </c>
       <c r="AN42" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
@@ -6958,10 +6954,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6984,13 +6980,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7041,7 +7037,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7056,13 +7052,13 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7073,10 +7069,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7102,10 +7098,10 @@
         <v>104</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7156,7 +7152,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7177,7 +7173,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7188,10 +7184,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7214,13 +7210,13 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7271,7 +7267,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7286,13 +7282,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7303,10 +7299,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7332,14 +7328,14 @@
         <v>166</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7388,7 +7384,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7403,13 +7399,13 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7420,10 +7416,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7446,16 +7442,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7481,14 +7477,14 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7505,7 +7501,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7526,7 +7522,7 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7537,10 +7533,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7563,13 +7559,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7620,7 +7616,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7635,13 +7631,13 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7652,10 +7648,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7678,13 +7674,13 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7735,7 +7731,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7750,13 +7746,13 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7767,10 +7763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7793,16 +7789,16 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7852,7 +7848,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7867,13 +7863,13 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7884,10 +7880,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7910,13 +7906,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7967,7 +7963,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7985,10 +7981,10 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -7999,10 +7995,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8025,13 +8021,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8082,7 +8078,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8103,7 +8099,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8114,10 +8110,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8143,10 +8139,10 @@
         <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>162</v>
@@ -8199,7 +8195,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8220,7 +8216,7 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8231,14 +8227,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8260,10 +8256,10 @@
         <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>162</v>
@@ -8318,7 +8314,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8350,10 +8346,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8376,16 +8372,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8435,7 +8431,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8456,7 +8452,7 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8467,10 +8463,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8493,13 +8489,13 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8550,7 +8546,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8571,7 +8567,7 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8582,10 +8578,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8611,10 +8607,10 @@
         <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>162</v>
@@ -8667,7 +8663,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8688,7 +8684,7 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8699,14 +8695,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8728,10 +8724,10 @@
         <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>162</v>
@@ -8786,7 +8782,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8818,10 +8814,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8844,13 +8840,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8901,7 +8897,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8922,7 +8918,7 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -8933,10 +8929,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8959,13 +8955,13 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9016,7 +9012,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9037,7 +9033,7 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9048,10 +9044,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9074,13 +9070,13 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9131,7 +9127,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9152,7 +9148,7 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
@@ -9163,10 +9159,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9189,19 +9185,19 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9250,7 +9246,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9268,10 +9264,10 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9282,10 +9278,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9308,16 +9304,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9367,7 +9363,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9385,24 +9381,24 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>461</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9425,13 +9421,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9482,7 +9478,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9500,24 +9496,24 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>467</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9540,16 +9536,16 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9599,7 +9595,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9617,10 +9613,10 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9631,10 +9627,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9657,13 +9653,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9714,7 +9710,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9735,10 +9731,10 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>21</v>
@@ -9746,10 +9742,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9772,13 +9768,13 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9829,7 +9825,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9847,10 +9843,10 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9861,10 +9857,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9887,13 +9883,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9944,7 +9940,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -9965,7 +9961,7 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9976,10 +9972,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10005,10 +10001,10 @@
         <v>135</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>162</v>
@@ -10061,7 +10057,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10082,7 +10078,7 @@
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10093,14 +10089,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10122,10 +10118,10 @@
         <v>135</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>162</v>
@@ -10180,7 +10176,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10212,10 +10208,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10238,16 +10234,16 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10273,14 +10269,14 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
       </c>
@@ -10297,7 +10293,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>90</v>
@@ -10315,24 +10311,24 @@
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>495</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10355,13 +10351,13 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10388,14 +10384,14 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
       </c>
@@ -10412,7 +10408,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10430,24 +10426,24 @@
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>503</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10470,13 +10466,13 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10527,7 +10523,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10542,13 +10538,13 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -10559,14 +10555,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10585,16 +10581,16 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10644,7 +10640,7 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10665,7 +10661,7 @@
         <v>21</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>21</v>
@@ -10676,10 +10672,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10702,16 +10698,16 @@
         <v>21</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10761,7 +10757,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10776,13 +10772,13 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>523</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$73</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2796" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2720" uniqueCount="529">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T15:59:40+00:00</t>
+    <t>2026-02-17T17:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -429,10 +429,64 @@
     <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>MedicationRequest.contained:medication</t>
+  </si>
+  <si>
+    <t>medication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medication {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication}
+</t>
+  </si>
+  <si>
+    <t>Definition of a Medication</t>
+  </si>
+  <si>
+    <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>
+  </si>
+  <si>
+    <t>NewRx/MedicationPrescribed+-or-+RxFill/MedicationDispensed+-or-+RxHistoryResponse/MedicationDispensed+-or-+RxHistoryResponse/MedicationPrescribed</t>
+  </si>
+  <si>
+    <t>ManufacturedProduct[classCode=ADMM]</t>
+  </si>
+  <si>
+    <t>MedicationRequest.contained:substance</t>
+  </si>
+  <si>
+    <t>substance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Substance {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-substance}
+</t>
+  </si>
+  <si>
+    <t>A homogeneous material with a definite composition</t>
+  </si>
+  <si>
+    <t>A homogeneous material with a definite composition.</t>
+  </si>
+  <si>
+    <t>Material</t>
   </si>
   <si>
     <t>MedicationRequest.extension</t>
@@ -450,9 +504,6 @@
   <si>
     <t xml:space="preserve">value:url}
 </t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -765,30 +816,18 @@
     <t>MedicationRequest.medication[x]</t>
   </si>
   <si>
-    <t>CodeableConcept
-Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)</t>
-  </si>
-  <si>
-    <t>Medication to be taken</t>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
+</t>
+  </si>
+  <si>
+    <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit 
+Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
   </si>
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the Medication resource is recommended.  For example, if you require form or lot number or if the medication is compounded or extemporaneously prepared, then you must reference the Medication resource.</t>
-  </si>
-  <si>
-    <t>A coded concept identifying substance or product that can be ordered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -812,21 +851,6 @@
     <t>RXE-2-Give Code / RXO-1-Requested Give Code / RXC-2-Component Code</t>
   </si>
   <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept</t>
-  </si>
-  <si>
-    <t>medicationCodeableConcept</t>
-  </si>
-  <si>
-    <t>Angabe mittels Pharmazentralnummer (PZN) aus der ASP-Liste.</t>
-  </si>
-  <si>
-    <t>https://termgit.elga.gv.at/CodeSystem/asp-liste</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.id</t>
-  </si>
-  <si>
     <t>MedicationRequest.medication[x].id</t>
   </si>
   <si>
@@ -846,9 +870,6 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.extension</t>
-  </si>
-  <si>
     <t>MedicationRequest.medication[x].extension</t>
   </si>
   <si>
@@ -864,75 +885,88 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
+    <t>MedicationRequest.medication[x].reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationReference</t>
-  </si>
-  <si>
-    <t>medicationReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
-</t>
-  </si>
-  <si>
-    <t>Bei magistralen Anwendungen oder Infusionen ohne PZN.</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+contained-ref:Medication must be contained (#...) {reference.startsWith('#')}</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x].display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
   </si>
   <si>
     <t>MedicationRequest.subject</t>
@@ -942,7 +976,8 @@
 </t>
   </si>
   <si>
-    <t>Österreichischer Patient für den die geplante Abgabe ausgestellt wird.</t>
+    <t>Patient, für den der Medikationsplaneintrag ausgestellt werden soll, der über den 
+Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Medikation ist.</t>
   </si>
   <si>
     <t>A link to a resource representing the person or set of individuals to whom the medication will be given.</t>
@@ -975,6 +1010,9 @@
 </t>
   </si>
   <si>
+    <t>Aufenthalt/Begegnung, während dessen die geplante Abgabe erstellt wurde. Keine Verwendung in der geplanten Abgabe.</t>
+  </si>
+  <si>
     <t>The Encounter during which this [x] was created or to which the creation of this record is tightly associated.</t>
   </si>
   <si>
@@ -1000,6 +1038,11 @@
 </t>
   </si>
   <si>
+    <t>Referenz auf zusätzliche Informationen (Ressource Any)
+(z. B. Größe und Gewicht des Patienten), die die Verschreibung des Medikaments unterstützen. 
+Keine Verwendung in der geplanten Abgabe.</t>
+  </si>
+  <si>
     <t>Include additional information (for example, patient height and weight) that supports the ordering of the medication.</t>
   </si>
   <si>
@@ -1044,7 +1087,8 @@
 </t>
   </si>
   <si>
-    <t>Der Arzt oder die Ärztin, die die geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist.</t>
+    <t>Der Arzt oder die Ärztin, die die geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist.
+Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen.</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -1116,7 +1160,7 @@
   </si>
   <si>
     <t>Grund für die Verordnung des Arzneimittels. 
-Entweder Code oder Referenz (evtl. Invariante).</t>
+Entweder Code oder Referenz (TODO: Evtl. Invariante). Erst wenn codierte Angabe möglich.</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -1144,18 +1188,6 @@
   </si>
   <si>
     <t>ORC-16-Order Control Code Reason /RXE-27-Give Indication/RXO-20-Indication / RXD-21-Indication / RXG-22-Indication / RXA-19-Indication</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode.coding</t>
-  </si>
-  <si>
-    <t>MedicationRequest.reasonCode.text</t>
   </si>
   <si>
     <t>MedicationRequest.reasonReference</t>
@@ -1165,6 +1197,9 @@
 </t>
   </si>
   <si>
+    <t>Condition or observation that supports why the prescription is being written</t>
+  </si>
+  <si>
     <t>Condition or observation that supports why the medication was ordered.</t>
   </si>
   <si>
@@ -1184,8 +1219,7 @@
 </t>
   </si>
   <si>
-    <t>URL, die auf ein Protokoll, eine Richtlinie, 
-eine Guideline oder eine andere Definition verweist, die von diesem 
+    <t>URL, die auf ein Protokoll (Richtlinie, Guideline) verweist, die von diesem 
 Medikationsplaneintrag ganz oder teilweise eingehalten wird. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
@@ -1201,8 +1235,7 @@
     <t>MedicationRequest.instantiatesUri</t>
   </si>
   <si>
-    <t>URL, die auf ein extern gepflegtes Protokoll, eine Richtlinie, eine Richtlinie, 
-eine Guideline oder eine andere Definition verweist, die von diesem 
+    <t>URL, die auf ein extern gepflegtes Protokoll (Richtlinie, Guideline) verweist, die von diesem 
 Medikationsplaneintrag ganz oder teilweise eingehalten wird. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
@@ -1292,7 +1325,7 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen zur geplanten Abgabe. TODO: zu prüfen im Kontext Korrekturvermerk</t>
+    <t>Zusätzliche Informationen zur geplanten Abgabe. TODO: prüfen</t>
   </si>
   <si>
     <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
@@ -1314,7 +1347,7 @@
 </t>
   </si>
   <si>
-    <t>TODO: alle Elemente + R5 Extensions prüfen</t>
+    <t>Anweisungen zur Einnahme/Verabreichung des Arzneimittels. TODO: alle Elemente + R5 Extensions prüfen</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -1541,9 +1574,10 @@
     <t>MedicationRequest.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob eine Substitution Teil der Abgabe sein kann / sollte / nicht sein darf. 
-Dieser Block erläutert die Absicht des verschreibenden Arztes. Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden. 
-TODO: Eher keine Verwendung in der geplanten Abgabe, Dokumentation über Substitution erfolg in der Dispenses-Resource.</t>
+    <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht.
+Erläutert die Absicht des verschreibenden Arztes. Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden. 
+Die Dokumentation über eine tatsächlich erfolgte Substitution erfolgt in der Dispense-Resource. 
+TODO: Eher keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -1646,7 +1680,7 @@
 </t>
   </si>
   <si>
-    <t>Referenenz auf DetectedIssue Ressource. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Klinisches Problem mit Maßnahme. Nur mittesl Referenz auf Ressouce DetectedIssue. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates an actual or potential clinical issue with or between one or more active or proposed clinical actions for a patient; e.g. Drug-drug interaction, duplicate therapy, dosage alert etc.</t>
@@ -1665,8 +1699,8 @@
 </t>
   </si>
   <si>
-    <t>Bezeichnet eine Liste von Provenance-Ressourcen, die verschiedene relevante Versionen 
-dieser Ressource dokumentieren. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Referenz auf Provenance-Ressourcen, die verschiedene relevante Versionen dieser Ressource dokumentieren. 
+Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Links to Provenance records for past versions of this resource or fulfilling request or event resources that identify key state transitions or updates that are likely to be relevant to a user looking at the current version of the resource.</t>
@@ -2003,12 +2037,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO75"/>
+  <dimension ref="A1:AO73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="58.75" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="51.68359375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.41015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2884,7 +2918,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>81</v>
@@ -2946,19 +2980,17 @@
         <v>21</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AC8" s="2"/>
       <c r="AD8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2979,7 +3011,7 @@
         <v>21</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>21</v>
@@ -2990,21 +3022,23 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C9" s="2"/>
+        <v>126</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="D9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -3016,15 +3050,17 @@
         <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>131</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -3061,17 +3097,19 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -3083,16 +3121,16 @@
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL9" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="AK9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AM9" t="s" s="2">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>21</v>
@@ -3103,13 +3141,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>21</v>
@@ -3119,7 +3157,7 @@
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
@@ -3131,15 +3169,17 @@
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>131</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
@@ -3188,7 +3228,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3197,10 +3237,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -3209,7 +3249,7 @@
         <v>21</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>21</v>
@@ -3220,14 +3260,12 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C11" t="s" s="2">
         <v>149</v>
       </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
@@ -3236,7 +3274,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -3293,19 +3331,17 @@
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3314,10 +3350,10 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>21</v>
@@ -3326,7 +3362,7 @@
         <v>21</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>21</v>
@@ -3337,13 +3373,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
@@ -3365,13 +3401,13 @@
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3422,7 +3458,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3431,10 +3467,10 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
@@ -3443,7 +3479,7 @@
         <v>21</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>21</v>
@@ -3454,46 +3490,44 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
@@ -3541,7 +3575,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3550,10 +3584,10 @@
         <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>21</v>
@@ -3562,7 +3596,7 @@
         <v>21</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>21</v>
@@ -3571,26 +3605,28 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G14" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="G14" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H14" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>21</v>
@@ -3599,17 +3635,15 @@
         <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3658,7 +3692,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3667,67 +3701,69 @@
         <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO14" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" hidden="true">
+      <c r="A15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AN14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>91</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
       </c>
@@ -3751,64 +3787,66 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Y15" s="2"/>
-      <c r="Z15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" hidden="true">
-      <c r="A16" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3816,13 +3854,13 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
@@ -3831,16 +3869,16 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3866,13 +3904,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3890,13 +3928,13 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
@@ -3905,27 +3943,27 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3951,13 +3989,13 @@
         <v>110</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3968,7 +4006,7 @@
         <v>21</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>21</v>
@@ -3983,13 +4021,11 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -4007,7 +4043,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -4022,27 +4058,27 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>21</v>
+        <v>196</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4050,13 +4086,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
@@ -4065,16 +4101,16 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4085,7 +4121,7 @@
         <v>21</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>209</v>
+        <v>21</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>21</v>
@@ -4100,13 +4136,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -4124,13 +4160,13 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
@@ -4139,27 +4175,27 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4167,16 +4203,16 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>91</v>
@@ -4185,12 +4221,14 @@
         <v>110</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -4200,7 +4238,7 @@
         <v>21</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>21</v>
@@ -4215,13 +4253,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -4239,10 +4277,10 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>90</v>
@@ -4254,27 +4292,27 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" hidden="true">
-      <c r="A20" t="s" s="2">
-        <v>222</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4282,31 +4320,31 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4317,7 +4355,7 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>21</v>
+        <v>223</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>21</v>
@@ -4332,13 +4370,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>21</v>
+        <v>224</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -4356,13 +4394,13 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
@@ -4374,13 +4412,13 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>227</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>21</v>
@@ -4414,13 +4452,13 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4447,13 +4485,13 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
@@ -4486,16 +4524,16 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>21</v>
+        <v>235</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>21</v>
@@ -4503,10 +4541,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4514,31 +4552,31 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I22" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4564,32 +4602,34 @@
         <v>21</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>239</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>90</v>
@@ -4601,31 +4641,29 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" hidden="true">
+      <c r="A23" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>247</v>
-      </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4634,10 +4672,10 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
@@ -4646,17 +4684,15 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>186</v>
+        <v>243</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4681,11 +4717,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>250</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4703,10 +4741,10 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>90</v>
@@ -4718,27 +4756,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4746,30 +4784,32 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4818,10 +4858,10 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>90</v>
@@ -4830,41 +4870,41 @@
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>21</v>
+        <v>253</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>21</v>
+        <v>255</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>21</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -4876,17 +4916,15 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>135</v>
+        <v>258</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M25" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4923,40 +4961,40 @@
         <v>21</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>21</v>
@@ -4967,18 +5005,18 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>81</v>
@@ -4990,23 +5028,21 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>266</v>
+        <v>150</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -5042,19 +5078,19 @@
         <v>21</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>21</v>
+        <v>266</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5066,7 +5102,7 @@
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>21</v>
@@ -5075,21 +5111,21 @@
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5112,20 +5148,18 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
       </c>
@@ -5173,7 +5207,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5182,10 +5216,10 @@
         <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>21</v>
+        <v>273</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>274</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>21</v>
@@ -5194,25 +5228,23 @@
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>281</v>
+        <v>135</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>282</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>21</v>
       </c>
@@ -5224,7 +5256,7 @@
         <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
@@ -5233,16 +5265,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>285</v>
+        <v>104</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5268,13 +5300,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>21</v>
+        <v>281</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -5292,10 +5324,10 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>233</v>
+        <v>282</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>90</v>
@@ -5307,27 +5339,27 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>244</v>
+        <v>135</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5335,13 +5367,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -5350,16 +5382,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>288</v>
+        <v>180</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5412,7 +5444,7 @@
         <v>287</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>90</v>
@@ -5424,27 +5456,27 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>293</v>
+        <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>295</v>
+        <v>21</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>296</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5455,7 +5487,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5464,19 +5496,19 @@
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>298</v>
+        <v>258</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5526,7 +5558,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5541,27 +5573,27 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>301</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>302</v>
+        <v>135</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>304</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5569,30 +5601,32 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>230</v>
+        <v>296</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5641,13 +5675,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5656,27 +5690,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>21</v>
+        <v>300</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="AN31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AO31" t="s" s="2">
-        <v>21</v>
-      </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5684,30 +5718,32 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -5756,7 +5792,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5771,27 +5807,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>315</v>
+        <v>196</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5799,28 +5835,28 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5871,13 +5907,13 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
@@ -5886,27 +5922,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5914,28 +5950,28 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>230</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5986,7 +6022,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6001,27 +6037,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
-      <c r="A35" t="s" s="2">
-        <v>331</v>
-      </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6029,13 +6065,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -6044,17 +6080,15 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>186</v>
+        <v>329</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>230</v>
+        <v>330</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -6079,13 +6113,13 @@
         <v>21</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>334</v>
+        <v>21</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>335</v>
+        <v>21</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>21</v>
@@ -6103,7 +6137,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6118,16 +6152,16 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>337</v>
+        <v>301</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>21</v>
+        <v>333</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>21</v>
@@ -6135,10 +6169,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6161,13 +6195,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6218,7 +6252,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6233,27 +6267,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6264,28 +6298,28 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K37" t="s" s="2">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>344</v>
+        <v>244</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6311,13 +6345,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -6335,13 +6369,13 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
@@ -6350,27 +6384,27 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>350</v>
+        <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>352</v>
+        <v>21</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>353</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6381,7 +6415,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -6393,13 +6427,13 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>253</v>
+        <v>348</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>255</v>
+        <v>349</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6450,7 +6484,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>256</v>
+        <v>347</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6462,7 +6496,7 @@
         <v>21</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>21</v>
@@ -6471,10 +6505,10 @@
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>257</v>
+        <v>350</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
@@ -6482,21 +6516,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>21</v>
@@ -6508,16 +6542,16 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>260</v>
+        <v>353</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>261</v>
+        <v>354</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>162</v>
+        <v>355</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6543,31 +6577,31 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>262</v>
+        <v>21</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>263</v>
+        <v>352</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6579,30 +6613,30 @@
         <v>21</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>21</v>
+        <v>358</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>257</v>
+        <v>360</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>21</v>
+        <v>362</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6610,7 +6644,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>81</v>
@@ -6622,23 +6656,21 @@
         <v>21</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>266</v>
+        <v>364</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>267</v>
+        <v>365</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>268</v>
+        <v>366</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
@@ -6686,7 +6718,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>271</v>
+        <v>363</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6701,27 +6733,27 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>21</v>
+        <v>368</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>21</v>
+        <v>196</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>272</v>
+        <v>369</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6732,7 +6764,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6744,20 +6776,16 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>253</v>
+        <v>371</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>276</v>
+        <v>372</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
       </c>
@@ -6805,13 +6833,13 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>280</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -6820,27 +6848,27 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>21</v>
+        <v>374</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>281</v>
+        <v>375</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>282</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6851,29 +6879,27 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I42" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K42" t="s" s="2">
-        <v>359</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6922,7 +6948,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6937,27 +6963,27 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>362</v>
+        <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>352</v>
+        <v>21</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6965,13 +6991,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6980,13 +7006,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7037,7 +7063,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7052,13 +7078,13 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7067,12 +7093,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7080,13 +7106,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -7095,16 +7121,18 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -7152,13 +7180,13 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -7167,13 +7195,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>21</v>
+        <v>389</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7182,12 +7210,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7195,30 +7223,32 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>374</v>
+        <v>200</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7243,13 +7273,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>21</v>
+        <v>396</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -7267,13 +7297,13 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
@@ -7282,13 +7312,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>377</v>
+        <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7297,12 +7327,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7310,33 +7340,31 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>166</v>
+        <v>399</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>380</v>
+        <v>244</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>382</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7384,13 +7412,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -7399,13 +7427,13 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7414,12 +7442,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7430,10 +7458,10 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
@@ -7442,17 +7470,15 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>186</v>
+        <v>404</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7477,13 +7503,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>389</v>
+        <v>21</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>390</v>
+        <v>21</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7501,13 +7527,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -7516,13 +7542,13 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>21</v>
+        <v>407</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>21</v>
+        <v>408</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7531,12 +7557,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7547,10 +7573,10 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
@@ -7559,15 +7585,17 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>230</v>
+        <v>412</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7616,7 +7644,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7631,13 +7659,13 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7648,10 +7676,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7662,7 +7690,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>91</v>
@@ -7674,13 +7702,13 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7731,13 +7759,13 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
@@ -7746,13 +7774,13 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7761,12 +7789,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7777,10 +7805,10 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -7789,17 +7817,15 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>405</v>
+        <v>258</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>406</v>
+        <v>259</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>21</v>
@@ -7848,28 +7874,28 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>404</v>
+        <v>261</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>409</v>
+        <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>410</v>
+        <v>262</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7878,26 +7904,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>21</v>
@@ -7906,15 +7932,17 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>412</v>
+        <v>150</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>413</v>
+        <v>264</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7963,28 +7991,28 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>411</v>
+        <v>267</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>415</v>
+        <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>416</v>
+        <v>262</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -7995,42 +8023,46 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>254</v>
+        <v>427</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -8078,19 +8110,19 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>256</v>
+        <v>429</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -8099,7 +8131,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>257</v>
+        <v>135</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8110,21 +8142,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -8136,16 +8168,16 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>135</v>
+        <v>418</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>260</v>
+        <v>431</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>261</v>
+        <v>432</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>162</v>
+        <v>433</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8195,19 +8227,19 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>263</v>
+        <v>430</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
@@ -8216,7 +8248,7 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>257</v>
+        <v>434</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8227,46 +8259,42 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>420</v>
+        <v>21</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>135</v>
+        <v>258</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>421</v>
+        <v>259</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8314,19 +8342,19 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>261</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
@@ -8335,7 +8363,7 @@
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>133</v>
+        <v>262</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8346,21 +8374,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -8372,16 +8400,16 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>412</v>
+        <v>150</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>425</v>
+        <v>264</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>426</v>
+        <v>265</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>427</v>
+        <v>176</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8431,19 +8459,19 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>424</v>
+        <v>267</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
@@ -8452,7 +8480,7 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>428</v>
+        <v>262</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8463,42 +8491,46 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>254</v>
+        <v>427</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8546,19 +8578,19 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>256</v>
+        <v>429</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
@@ -8567,7 +8599,7 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>257</v>
+        <v>135</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8578,21 +8610,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -8604,17 +8636,15 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>135</v>
+        <v>439</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>260</v>
+        <v>440</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
@@ -8663,19 +8693,19 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>263</v>
+        <v>438</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
@@ -8684,7 +8714,7 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>257</v>
+        <v>442</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8695,46 +8725,42 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>420</v>
+        <v>21</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>135</v>
+        <v>444</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8782,19 +8808,19 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
@@ -8803,7 +8829,7 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>133</v>
+        <v>447</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8814,10 +8840,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8840,13 +8866,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8897,7 +8923,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8918,7 +8944,7 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -8929,10 +8955,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8955,16 +8981,20 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -9012,7 +9042,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9030,10 +9060,10 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>21</v>
+        <v>457</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9044,10 +9074,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9070,15 +9100,17 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9127,7 +9159,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9145,24 +9177,24 @@
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>21</v>
+        <v>464</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>441</v>
+        <v>465</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9185,20 +9217,16 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9246,7 +9274,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>445</v>
+        <v>467</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9264,24 +9292,24 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>21</v>
+        <v>472</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9304,16 +9332,16 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9363,7 +9391,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9381,24 +9409,24 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>459</v>
+        <v>478</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>460</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9421,13 +9449,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>433</v>
+        <v>480</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>463</v>
+        <v>482</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9478,7 +9506,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9496,24 +9524,24 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>464</v>
+        <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>466</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9527,7 +9555,7 @@
         <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>21</v>
@@ -9536,17 +9564,15 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -9595,7 +9621,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9613,10 +9639,10 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9627,10 +9653,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9653,13 +9679,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>474</v>
+        <v>258</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>475</v>
+        <v>259</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>476</v>
+        <v>260</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9710,7 +9736,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>473</v>
+        <v>261</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9722,7 +9748,7 @@
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
@@ -9731,35 +9757,35 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>477</v>
+        <v>262</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>21</v>
@@ -9768,15 +9794,17 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>412</v>
+        <v>150</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>479</v>
+        <v>264</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9825,28 +9853,28 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>478</v>
+        <v>267</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>481</v>
+        <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>482</v>
+        <v>262</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9857,42 +9885,46 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>253</v>
+        <v>150</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>254</v>
+        <v>427</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
       </c>
@@ -9940,19 +9972,19 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>256</v>
+        <v>429</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
@@ -9961,7 +9993,7 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>257</v>
+        <v>135</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9972,21 +10004,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -9998,16 +10030,16 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>135</v>
+        <v>493</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>260</v>
+        <v>494</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>261</v>
+        <v>495</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>162</v>
+        <v>496</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10033,13 +10065,13 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>21</v>
+        <v>497</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>21</v>
+        <v>498</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -10057,78 +10089,74 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>263</v>
+        <v>492</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>21</v>
+        <v>487</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>257</v>
+        <v>499</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>21</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>420</v>
+        <v>21</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>135</v>
+        <v>200</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>421</v>
+        <v>502</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -10152,13 +10180,13 @@
         <v>21</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>21</v>
+        <v>504</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>21</v>
+        <v>505</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -10176,42 +10204,42 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>423</v>
+        <v>501</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>21</v>
+        <v>506</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>133</v>
+        <v>507</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>21</v>
+        <v>508</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>486</v>
+        <v>509</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>486</v>
+        <v>509</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10219,13 +10247,13 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
@@ -10234,17 +10262,15 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>487</v>
+        <v>510</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>488</v>
+        <v>511</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>512</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
@@ -10269,13 +10295,13 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>491</v>
+        <v>21</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>492</v>
+        <v>21</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -10293,10 +10319,10 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>486</v>
+        <v>509</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>90</v>
@@ -10308,38 +10334,38 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>21</v>
+        <v>513</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>494</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>21</v>
+        <v>516</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>21</v>
@@ -10351,15 +10377,17 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>186</v>
+        <v>517</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>496</v>
+        <v>518</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -10384,13 +10412,13 @@
         <v>21</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>498</v>
+        <v>21</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>499</v>
+        <v>21</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>21</v>
@@ -10408,13 +10436,13 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>21</v>
@@ -10426,24 +10454,24 @@
         <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>502</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10454,10 +10482,10 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>21</v>
@@ -10466,15 +10494,17 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>504</v>
+        <v>523</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -10523,13 +10553,13 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
@@ -10538,257 +10568,23 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO75" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO75">
+  <autoFilter ref="A1:AO73">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10798,7 +10594,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
+  <conditionalFormatting sqref="A2:AI72">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$74</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2720" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2757" uniqueCount="542">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T17:15:57+00:00</t>
+    <t>2026-02-20T10:02:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -816,18 +816,26 @@
     <t>MedicationRequest.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
+    <t xml:space="preserve">Reference(Medication|4.0.1)
 </t>
   </si>
   <si>
-    <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit 
-Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
+    <t>Medication to be taken</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
   </si>
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the Medication resource is recommended.  For example, if you require form or lot number or if the medication is compounded or extemporaneously prepared, then you must reference the Medication resource.</t>
+  </si>
+  <si>
+    <t>A coded concept identifying substance or product that can be ordered.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>closed</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -851,6 +859,23 @@
     <t>RXE-2-Give Code / RXO-1-Requested Give Code / RXC-2-Component Code</t>
   </si>
   <si>
+    <t>MedicationRequest.medication[x]:medicationReference</t>
+  </si>
+  <si>
+    <t>medicationReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
+</t>
+  </si>
+  <si>
+    <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit 
+Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationReference.id</t>
+  </si>
+  <si>
     <t>MedicationRequest.medication[x].id</t>
   </si>
   <si>
@@ -870,6 +895,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>MedicationRequest.medication[x]:medicationReference.extension</t>
+  </si>
+  <si>
     <t>MedicationRequest.medication[x].extension</t>
   </si>
   <si>
@@ -883,6 +911,9 @@
   </si>
   <si>
     <t>Element.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationReference.reference</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x].reference</t>
@@ -905,7 +936,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-contained-ref:Medication must be contained (#...) {reference.startsWith('#')}</t>
+contained-ref:Medication must be contained (#...) {$this.startsWith('#')}</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationReference.type</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x].type</t>
@@ -931,6 +965,9 @@
   </si>
   <si>
     <t>Reference.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationReference.identifier</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x].identifier</t>
@@ -952,6 +989,9 @@
   </si>
   <si>
     <t>.identifier</t>
+  </si>
+  <si>
+    <t>MedicationRequest.medication[x]:medicationReference.display</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x].display</t>
@@ -2037,10 +2077,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO73"/>
+  <dimension ref="A1:AO74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="52.8828125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="51.68359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.41015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -4771,7 +4811,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>247</v>
       </c>
@@ -4834,28 +4874,26 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>21</v>
+        <v>253</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>21</v>
+        <v>254</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>247</v>
@@ -4873,58 +4911,62 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4973,10 +5015,10 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>90</v>
@@ -4985,41 +5027,41 @@
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>21</v>
+        <v>255</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>21</v>
+        <v>256</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>21</v>
+        <v>258</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>21</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -5031,17 +5073,15 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>150</v>
+        <v>266</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -5078,31 +5118,31 @@
         <v>21</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>266</v>
+        <v>21</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>21</v>
@@ -5111,7 +5151,7 @@
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>21</v>
@@ -5122,21 +5162,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
@@ -5145,19 +5185,19 @@
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>258</v>
+        <v>150</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>271</v>
+        <v>176</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5195,31 +5235,31 @@
         <v>21</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>273</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>274</v>
+        <v>155</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>21</v>
@@ -5228,7 +5268,7 @@
         <v>21</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>21</v>
@@ -5239,10 +5279,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5265,16 +5305,16 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5300,13 +5340,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>280</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>281</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -5333,10 +5373,10 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>21</v>
+        <v>283</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>284</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>21</v>
@@ -5356,10 +5396,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5382,16 +5422,16 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5417,13 +5457,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>21</v>
+        <v>291</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5441,7 +5481,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5462,7 +5502,7 @@
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>288</v>
+        <v>135</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>21</v>
@@ -5473,10 +5513,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5499,16 +5539,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>258</v>
+        <v>180</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5558,7 +5598,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5579,7 +5619,7 @@
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
@@ -5588,12 +5628,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5601,13 +5641,13 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -5616,16 +5656,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5675,10 +5715,10 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>90</v>
@@ -5690,27 +5730,27 @@
         <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>299</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>300</v>
+        <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>301</v>
+        <v>135</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>302</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>303</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5718,31 +5758,31 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5792,10 +5832,10 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>90</v>
@@ -5807,27 +5847,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>196</v>
+        <v>313</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5850,15 +5890,17 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -5907,13 +5949,13 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
@@ -5922,27 +5964,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>21</v>
+        <v>196</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>21</v>
+        <v>325</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5950,28 +5992,28 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6022,13 +6064,13 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
@@ -6037,27 +6079,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="AM34" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="AO34" t="s" s="2">
-        <v>327</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6080,13 +6122,13 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6137,7 +6179,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6152,27 +6194,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>301</v>
+        <v>338</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>21</v>
+        <v>340</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6180,28 +6222,28 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>244</v>
+        <v>343</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6252,7 +6294,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6267,16 +6309,16 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
@@ -6284,10 +6326,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6307,20 +6349,18 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>200</v>
+        <v>348</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>244</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6345,13 +6385,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>343</v>
+        <v>21</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -6369,7 +6409,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6384,16 +6424,16 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>21</v>
+        <v>352</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6401,10 +6441,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6424,18 +6464,20 @@
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>348</v>
+        <v>200</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>244</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>21</v>
@@ -6460,13 +6502,13 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6484,7 +6526,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6499,16 +6541,16 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>21</v>
+        <v>358</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>351</v>
+        <v>21</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
@@ -6516,10 +6558,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6542,17 +6584,15 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>200</v>
+        <v>361</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>353</v>
+        <v>244</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6577,13 +6617,13 @@
         <v>21</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>357</v>
+        <v>21</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>21</v>
@@ -6601,13 +6641,13 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6616,27 +6656,27 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>359</v>
+        <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>362</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6647,7 +6687,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -6659,16 +6699,16 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>364</v>
+        <v>200</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6694,13 +6734,13 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -6718,7 +6758,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6733,27 +6773,27 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>196</v>
+        <v>372</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>21</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6764,7 +6804,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6773,18 +6813,20 @@
         <v>21</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6833,7 +6875,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6848,16 +6890,16 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -6865,10 +6907,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6891,13 +6933,13 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>104</v>
+        <v>384</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6948,7 +6990,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6963,13 +7005,13 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>21</v>
+        <v>387</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -6978,12 +7020,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6991,13 +7033,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -7006,13 +7048,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>380</v>
+        <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7063,7 +7105,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7078,13 +7120,13 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>383</v>
+        <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7095,10 +7137,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7121,18 +7163,16 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>180</v>
+        <v>393</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>388</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -7180,13 +7220,13 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
@@ -7195,13 +7235,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7210,12 +7250,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7223,33 +7263,33 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -7273,13 +7313,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>396</v>
+        <v>21</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -7297,7 +7337,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7312,13 +7352,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>21</v>
+        <v>402</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7329,10 +7369,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7355,15 +7395,17 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>399</v>
+        <v>200</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>244</v>
+        <v>405</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7388,13 +7430,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>21</v>
+        <v>408</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>21</v>
+        <v>409</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7412,13 +7454,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -7427,13 +7469,13 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>401</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7442,12 +7484,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7458,10 +7500,10 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
@@ -7470,13 +7512,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>405</v>
+        <v>244</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7527,7 +7569,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7542,13 +7584,13 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>408</v>
+        <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7559,10 +7601,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7585,17 +7627,15 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7644,7 +7684,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7659,13 +7699,13 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>21</v>
+        <v>421</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7676,10 +7716,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7690,7 +7730,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>91</v>
@@ -7702,15 +7742,17 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7759,13 +7801,13 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>21</v>
@@ -7774,13 +7816,13 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>421</v>
+        <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7789,12 +7831,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7808,7 +7850,7 @@
         <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -7817,13 +7859,13 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>258</v>
+        <v>431</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>259</v>
+        <v>432</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>260</v>
+        <v>433</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7874,7 +7916,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>261</v>
+        <v>430</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7886,16 +7928,16 @@
         <v>21</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>262</v>
+        <v>435</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7906,21 +7948,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -7932,17 +7974,15 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>150</v>
+        <v>266</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>21</v>
@@ -7991,19 +8031,19 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
@@ -8012,7 +8052,7 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8023,14 +8063,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>426</v>
+        <v>173</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8043,26 +8083,24 @@
         <v>21</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>150</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>427</v>
+        <v>273</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>428</v>
+        <v>274</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="O52" t="s" s="2">
-        <v>177</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
       </c>
@@ -8110,7 +8148,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>429</v>
+        <v>276</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8131,7 +8169,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8142,44 +8180,46 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>418</v>
+        <v>150</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -8227,19 +8267,19 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
@@ -8248,7 +8288,7 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>434</v>
+        <v>135</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8259,10 +8299,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8285,15 +8325,17 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>258</v>
+        <v>431</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>259</v>
+        <v>444</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>21</v>
@@ -8342,7 +8384,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>261</v>
+        <v>443</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8354,7 +8396,7 @@
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
@@ -8363,7 +8405,7 @@
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>262</v>
+        <v>447</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8374,21 +8416,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>21</v>
@@ -8400,17 +8442,15 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>150</v>
+        <v>266</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8459,19 +8499,19 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
@@ -8480,7 +8520,7 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8491,14 +8531,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>426</v>
+        <v>173</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8511,26 +8551,24 @@
         <v>21</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>150</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>427</v>
+        <v>273</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>428</v>
+        <v>274</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="O56" t="s" s="2">
-        <v>177</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>21</v>
       </c>
@@ -8578,7 +8616,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>429</v>
+        <v>276</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8599,7 +8637,7 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8610,33 +8648,33 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>439</v>
+        <v>150</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>440</v>
@@ -8644,8 +8682,12 @@
       <c r="M57" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="N57" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8693,19 +8735,19 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
@@ -8714,7 +8756,7 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>442</v>
+        <v>135</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8725,10 +8767,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8751,13 +8793,13 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8808,7 +8850,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8829,7 +8871,7 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8840,10 +8882,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8866,13 +8908,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8923,7 +8965,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8944,7 +8986,7 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
@@ -8955,10 +8997,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8981,20 +9023,16 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
@@ -9042,7 +9080,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9060,10 +9098,10 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>457</v>
+        <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9074,10 +9112,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9100,18 +9138,20 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
       </c>
@@ -9159,7 +9199,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9177,24 +9217,24 @@
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>466</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9217,15 +9257,17 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>439</v>
+        <v>473</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>475</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9274,7 +9316,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9292,24 +9334,24 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9332,17 +9374,15 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>476</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9391,7 +9431,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9409,24 +9449,24 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>21</v>
+        <v>485</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9449,15 +9489,17 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>480</v>
+        <v>457</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -9506,7 +9548,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9524,24 +9566,24 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>21</v>
+        <v>490</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>351</v>
+        <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9555,7 +9597,7 @@
         <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>21</v>
@@ -9564,13 +9606,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>418</v>
+        <v>493</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9621,7 +9663,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9639,24 +9681,24 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>487</v>
+        <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9670,7 +9712,7 @@
         <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>21</v>
@@ -9679,13 +9721,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>258</v>
+        <v>431</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>259</v>
+        <v>498</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>260</v>
+        <v>499</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9736,7 +9778,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>261</v>
+        <v>497</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9748,16 +9790,16 @@
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>262</v>
+        <v>501</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9768,21 +9810,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -9794,17 +9836,15 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>150</v>
+        <v>266</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
@@ -9853,19 +9893,19 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>21</v>
@@ -9874,7 +9914,7 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9885,14 +9925,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>426</v>
+        <v>173</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9905,26 +9945,24 @@
         <v>21</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>150</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>427</v>
+        <v>273</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>428</v>
+        <v>274</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="O68" t="s" s="2">
-        <v>177</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>21</v>
       </c>
@@ -9972,7 +10010,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>429</v>
+        <v>276</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -9993,7 +10031,7 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -10004,44 +10042,46 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>493</v>
+        <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>494</v>
+        <v>440</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>495</v>
+        <v>441</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -10065,13 +10105,13 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>497</v>
+        <v>21</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>498</v>
+        <v>21</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -10089,42 +10129,42 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>492</v>
+        <v>442</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>487</v>
+        <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>499</v>
+        <v>135</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>500</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10132,7 +10172,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>90</v>
@@ -10147,15 +10187,17 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>200</v>
+        <v>506</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>509</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
@@ -10183,31 +10225,31 @@
         <v>204</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="Z70" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AA70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>501</v>
-      </c>
       <c r="AG70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>90</v>
@@ -10222,24 +10264,24 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10253,7 +10295,7 @@
         <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>21</v>
@@ -10262,13 +10304,13 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>510</v>
+        <v>200</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10295,13 +10337,13 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>21</v>
+        <v>204</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>21</v>
+        <v>517</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>21</v>
+        <v>518</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -10319,7 +10361,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10334,41 +10376,41 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>513</v>
+        <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>21</v>
+        <v>521</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>516</v>
+        <v>21</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>21</v>
@@ -10377,17 +10419,15 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -10436,13 +10476,13 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>21</v>
@@ -10451,13 +10491,13 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>21</v>
+        <v>526</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>21</v>
+        <v>519</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
@@ -10468,14 +10508,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>21</v>
+        <v>529</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10494,16 +10534,16 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10553,7 +10593,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10568,23 +10608,140 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>527</v>
+        <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO73" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO74" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO73">
+  <autoFilter ref="A1:AO74">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10594,7 +10751,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI72">
+  <conditionalFormatting sqref="A2:AI73">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T10:02:53+00:00</t>
+    <t>2026-02-23T08:57:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T08:57:08+00:00</t>
+    <t>2026-02-23T17:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1383,11 +1383,11 @@
     <t>MedicationRequest.dosageInstruction</t>
   </si>
   <si>
-    <t xml:space="preserve">Dosage
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-dosage}
 </t>
   </si>
   <si>
-    <t>Anweisungen zur Einnahme/Verabreichung des Arzneimittels. TODO: alle Elemente + R5 Extensions prüfen</t>
+    <t>Angabe der Dosierinformationen strukturiert oder als Freitext</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>81</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:25:44+00:00</t>
+    <t>2026-02-26T16:36:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet eine geplante Abgabe eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
+    <t>Bildet eine geplante Abgabe eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
 Sie enthält das verordnete Arzneimittel und dessen Dosierung und spielgelt die Inhalte des e-Rezepts wider. Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation.
 Als groupIdentifier dient die Geplante-Abgabe-ID (früher eMED-ID), die auch im e-Rezept mitgeführt wird.
 Werden mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer'). Verwendet R5 Backport Extensions.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:36:39+00:00</t>
+    <t>2026-03-03T08:59:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T08:59:33+00:00</t>
+    <t>2026-03-03T14:03:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T14:03:22+00:00</t>
+    <t>2026-03-05T12:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T12:55:37+00:00</t>
+    <t>2026-03-05T13:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:31:59+00:00</t>
+    <t>2026-03-06T12:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -734,6 +734,7 @@
   &lt;coding&gt;
     &lt;system value="https://fhir.hl7.at/elga/emed/r4/CodeSystem/MedicationRequestCategoryCS"/&gt;
     &lt;code value="2"/&gt;
+    &lt;display value="Geplante Abgabe"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$81</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2757" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3018" uniqueCount="584">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T12:22:28+00:00</t>
+    <t>2026-03-06T14:18:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -595,8 +595,9 @@
 </t>
   </si>
   <si>
-    <t>MedicationRequest identifier = {eMed-ID}_{locally assigned ID}.
-Setzt sich zusammen aus: groupIdentifier (Rezept-Klammer) und individueller Identifikation der geplanten Abgabe.</t>
+    <t>Gepante-Abgabe-ID = {groupIdentifier}_{Medikationsplaneintrag-ID}.
+Setzt sich zusammen aus: groupIdentifier (Rezept-Klammer) und Medikationsplaneintrag-ID.
+Wenn mehrere Medikamente gleichzeitig verordnet wurden, haben sie den gleichen groupIdentifier, aber unterschiedliche Medikationsplaneintrag-IDs.</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -720,8 +721,7 @@
     <t>MedicationRequest.category</t>
   </si>
   <si>
-    <t>Kategorie damit Instanz einer geplanten Abgabe von Medikationsplaneintrag
- unterschieden werden kann (beide haben intent order)</t>
+    <t>Kategorie zur Unterscheidung eines Medikationsplaneintrags von einer geplanten Abgabe (beide haben intent order)</t>
   </si>
   <si>
     <t>Indicates the type of medication request (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -1017,7 +1017,7 @@
 </t>
   </si>
   <si>
-    <t>Patient, für den der Medikationsplaneintrag ausgestellt werden soll, der über den 
+    <t>Patient, für den die geplante Abgabe ausgestellt werden soll, der über den 
 Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Medikation ist.</t>
   </si>
   <si>
@@ -1388,7 +1388,7 @@
 </t>
   </si>
   <si>
-    <t>Angabe der Dosierinformationen strukturiert oder als Freitext</t>
+    <t>Angabe der Dosierinformationen strukturiert oder als Freitext. TODO: Inhalte AtEmedDosage fachlich prüfen.</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -1410,7 +1410,7 @@
 </t>
   </si>
   <si>
-    <t>Details zur geplanten Abgabe des Arzneimittels.</t>
+    <t>Details zur geplanten Abgabe des Arzneimittels. TODO: alle Elemente fachlich zu prüfen.</t>
   </si>
   <si>
     <t>Indicates the specific details for the dispense or medication supply part of a medication request (also known as a Medication Prescription or Medication Order).  Note that this information is not always sent with the order.  There may be in some settings (e.g. hospitals) institutional or system support for completing the dispense details in the pharmacy department.</t>
@@ -1476,7 +1476,7 @@
 </t>
   </si>
   <si>
-    <t>First fill quantity</t>
+    <t>Anzahl der Einheiten für die erste Abgabe, z.B. 30 Kapseln oder 100 mg.</t>
   </si>
   <si>
     <t>The amount or quantity to provide as part of the first dispense.</t>
@@ -1504,7 +1504,7 @@
     <t>MedicationRequest.dispenseRequest.dispenseInterval</t>
   </si>
   <si>
-    <t>Minimum period of time between dispenses</t>
+    <t>Mindestzeitraum zwischen den Abgaben.</t>
   </si>
   <si>
     <t>The minimum period of time that must occur between dispenses of the medication.</t>
@@ -1517,7 +1517,7 @@
 </t>
   </si>
   <si>
-    <t>Time period supply is authorized for</t>
+    <t>Zeitraum in dem die geplante Abgabe eingelöst werden kann.</t>
   </si>
   <si>
     <t>This indicates the validity period of a prescription (stale dating the Prescription).</t>
@@ -1542,7 +1542,7 @@
 </t>
   </si>
   <si>
-    <t>Anzahl der möglichen Einlösungen.</t>
+    <t>Anzahl der weiteren möglichen Einlösungen.</t>
   </si>
   <si>
     <t>An integer indicating the number of times, in addition to the original dispense, (aka refills or repeats) that the patient can receive the prescribed medication. Usage Notes: This integer does not include the original order dispense. This means that if an order indicates dispense 30 tablets plus "3 repeats", then the order can be dispensed a total of 4 times and the patient can receive a total of 120 tablets.  A prescriber may explicitly say that zero refills are permitted after the initial dispense.</t>
@@ -1563,7 +1563,7 @@
     <t>MedicationRequest.dispenseRequest.quantity</t>
   </si>
   <si>
-    <t>Amount of medication to supply per dispense</t>
+    <t>Menge des Medikaments, die bei jeder Abgabe bereitgestellt werden soll, z.B. 30 Stück.</t>
   </si>
   <si>
     <t>The amount that is to be dispensed for one fill.</t>
@@ -1594,6 +1594,134 @@
   </si>
   <si>
     <t>expectedUseTime</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Dauer, für die die bereitgestellte Menge des Medikaments voraussichtlich ausreicht, z.B. 30 Tage.</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
+  </si>
+  <si>
+    <t>SN.2  / CQ - N/A</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.comparator</t>
+  </si>
+  <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
+    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
+  </si>
+  <si>
+    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>If there is no comparator, then there is no modification of the value</t>
+  </si>
+  <si>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+  </si>
+  <si>
+    <t>Quantity.comparator</t>
+  </si>
+  <si>
+    <t>IVL properties</t>
+  </si>
+  <si>
+    <t>SN.1  / CQ.1</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.unit</t>
+  </si>
+  <si>
+    <t>Unit representation</t>
+  </si>
+  <si>
+    <t>A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+  </si>
+  <si>
+    <t>Quantity.unit</t>
+  </si>
+  <si>
+    <t>PQ.unit</t>
+  </si>
+  <si>
+    <t>(see OBX.6 etc.) / CQ.2</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.system</t>
+  </si>
+  <si>
+    <t>System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Quantity.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty-3
+</t>
+  </si>
+  <si>
+    <t>CO.codeSystem, PQ.translation.codeSystem</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.code</t>
+  </si>
+  <si>
+    <t>Coded form of the unit</t>
+  </si>
+  <si>
+    <t>A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.performer</t>
@@ -1603,7 +1731,7 @@
 </t>
   </si>
   <si>
-    <t>Intended dispenser</t>
+    <t>Apotheke oder andere Einrichtung, die die geplante Abgabe einlösen soll. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates the intended dispensing Organization specified by the prescriber.</t>
@@ -2078,11 +2206,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO74"/>
+  <dimension ref="A1:AO81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.8828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="51.68359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="59.5390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.41015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -8298,7 +8426,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>443</v>
       </c>
@@ -8317,7 +8445,7 @@
         <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>21</v>
@@ -8996,7 +9124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>461</v>
       </c>
@@ -9015,7 +9143,7 @@
         <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>21</v>
@@ -9111,7 +9239,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>464</v>
       </c>
@@ -9130,7 +9258,7 @@
         <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>21</v>
@@ -9230,7 +9358,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>472</v>
       </c>
@@ -9249,7 +9377,7 @@
         <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>21</v>
@@ -9347,7 +9475,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>480</v>
       </c>
@@ -9366,7 +9494,7 @@
         <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>21</v>
@@ -9462,7 +9590,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>486</v>
       </c>
@@ -9481,7 +9609,7 @@
         <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
@@ -9607,13 +9735,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>493</v>
+        <v>266</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>494</v>
+        <v>267</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>495</v>
+        <v>268</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9664,7 +9792,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>492</v>
+        <v>269</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9676,7 +9804,7 @@
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
@@ -9685,35 +9813,35 @@
         <v>21</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>496</v>
+        <v>270</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>21</v>
@@ -9722,15 +9850,17 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>431</v>
+        <v>150</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>498</v>
+        <v>273</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9767,40 +9897,40 @@
         <v>21</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>497</v>
+        <v>276</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>501</v>
+        <v>270</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9811,10 +9941,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9834,19 +9964,23 @@
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>266</v>
+        <v>495</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>267</v>
+        <v>496</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -9894,7 +10028,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>269</v>
+        <v>500</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9906,7 +10040,7 @@
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>21</v>
@@ -9915,13 +10049,13 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>270</v>
+        <v>501</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>21</v>
+        <v>502</v>
       </c>
     </row>
     <row r="68" hidden="true">
@@ -9933,41 +10067,43 @@
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>273</v>
+        <v>504</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>505</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q68" s="2"/>
+      <c r="Q68" t="s" s="2">
+        <v>507</v>
+      </c>
       <c r="R68" t="s" s="2">
         <v>21</v>
       </c>
@@ -9987,13 +10123,13 @@
         <v>21</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>21</v>
+        <v>508</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>21</v>
+        <v>509</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>21</v>
@@ -10011,19 +10147,19 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>276</v>
+        <v>510</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
@@ -10032,56 +10168,54 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>270</v>
+        <v>511</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>21</v>
+        <v>512</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>439</v>
+        <v>21</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>150</v>
+        <v>266</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>440</v>
+        <v>514</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>515</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>177</v>
+        <v>516</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>21</v>
@@ -10130,19 +10264,19 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>442</v>
+        <v>517</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
@@ -10151,21 +10285,21 @@
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>135</v>
+        <v>518</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>21</v>
+        <v>519</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10173,7 +10307,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>90</v>
@@ -10185,21 +10319,21 @@
         <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>506</v>
+        <v>104</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -10223,13 +10357,13 @@
         <v>21</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>510</v>
+        <v>21</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>511</v>
+        <v>21</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -10247,16 +10381,16 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>21</v>
+        <v>525</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>102</v>
@@ -10265,24 +10399,24 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10302,19 +10436,23 @@
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>529</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>531</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -10338,13 +10476,13 @@
         <v>21</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>517</v>
+        <v>21</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>518</v>
+        <v>21</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>21</v>
@@ -10362,7 +10500,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10380,24 +10518,24 @@
         <v>21</v>
       </c>
       <c r="AL71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AM71" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>521</v>
-      </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10408,10 +10546,10 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>21</v>
@@ -10420,13 +10558,13 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10477,7 +10615,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10492,41 +10630,41 @@
         <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>526</v>
+        <v>21</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>519</v>
+        <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>529</v>
+        <v>21</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>21</v>
@@ -10535,17 +10673,15 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>530</v>
+        <v>431</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>533</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -10594,13 +10730,13 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
@@ -10612,10 +10748,10 @@
         <v>21</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>21</v>
+        <v>542</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
@@ -10626,10 +10762,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10640,7 +10776,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>21</v>
@@ -10652,17 +10788,15 @@
         <v>21</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>536</v>
+        <v>266</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>537</v>
+        <v>267</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>21</v>
@@ -10711,38 +10845,855 @@
         <v>21</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>535</v>
+        <v>269</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G75" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
+      <c r="H75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK74" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO74" t="s" s="2">
+      <c r="AK77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO74">
+  <autoFilter ref="A1:AO81">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10752,7 +11703,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI73">
+  <conditionalFormatting sqref="A2:AI80">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:18:10+00:00</t>
+    <t>2026-03-09T08:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T08:14:04+00:00</t>
+    <t>2026-03-09T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:03:26+00:00</t>
+    <t>2026-03-09T11:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:27:52+00:00</t>
+    <t>2026-03-10T08:28:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T08:28:41+00:00</t>
+    <t>2026-03-10T11:00:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -89,7 +89,7 @@
   <si>
     <t>Bildet eine geplante Abgabe eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
 Sie enthält das verordnete Arzneimittel und dessen Dosierung und spielgelt die Inhalte des e-Rezepts wider. Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation.
-Als groupIdentifier dient die Geplante-Abgabe-ID (früher eMED-ID), die auch im e-Rezept mitgeführt wird.
+Als groupIdentifier dient die Geplante-Abgabe-ID, die auch im e-Rezept mitgeführt wird.
 Werden mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer'). Verwendet R5 Backport Extensions.</t>
   </si>
   <si>
@@ -595,9 +595,7 @@
 </t>
   </si>
   <si>
-    <t>Gepante-Abgabe-ID = {groupIdentifier}_{Medikationsplaneintrag-ID}.
-Setzt sich zusammen aus: groupIdentifier (Rezept-Klammer) und Medikationsplaneintrag-ID.
-Wenn mehrere Medikamente gleichzeitig verordnet wurden, haben sie den gleichen groupIdentifier, aber unterschiedliche Medikationsplaneintrag-IDs.</t>
+    <t>Gepante-Abgabe-ID ? Verwendung prüfen.</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -1017,8 +1015,7 @@
 </t>
   </si>
   <si>
-    <t>Patient, für den die geplante Abgabe ausgestellt werden soll, der über den 
-Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Medikation ist.</t>
+    <t>Patient, für den die geplante Abgabe ausgestellt werden soll (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
   </si>
   <si>
     <t>A link to a resource representing the person or set of individuals to whom the medication will be given.</t>
@@ -1128,8 +1125,8 @@
 </t>
   </si>
   <si>
-    <t>Der Arzt oder die Ärztin, die die geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist.
-Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen.</t>
+    <t>Der Arzt oder die Ärztin, die die geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist 
+(eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen)</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -1201,7 +1198,7 @@
   </si>
   <si>
     <t>Grund für die Verordnung des Arzneimittels. 
-Entweder Code oder Referenz (TODO: Evtl. Invariante). Erst wenn codierte Angabe möglich.</t>
+Entweder Code oder Referenz (TODO: Evtl. Invariante). Verwendung in geplanter Abgabe prüfen.</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -1260,8 +1257,8 @@
 </t>
   </si>
   <si>
-    <t>URL, die auf ein Protokoll (Richtlinie, Guideline) verweist, die von diesem 
-Medikationsplaneintrag ganz oder teilweise eingehalten wird. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>URL, die auf ein Protokoll (Richtlinie, Guideline) verweist, das von dieser 
+geplanten Abgabe ganz oder teilweise eingehalten wird. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The URL pointing to a protocol, guideline, orderset, or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
@@ -1276,8 +1273,8 @@
     <t>MedicationRequest.instantiatesUri</t>
   </si>
   <si>
-    <t>URL, die auf ein extern gepflegtes Protokoll (Richtlinie, Guideline) verweist, die von diesem 
-Medikationsplaneintrag ganz oder teilweise eingehalten wird. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>URL, die auf ein extern gepflegtes Protokoll (Richtlinie, Guideline) verweist, das von dieser 
+geplanten Abgabe ganz oder teilweise eingehalten wird. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
@@ -1305,8 +1302,8 @@
     <t>MedicationRequest.groupIdentifier</t>
   </si>
   <si>
-    <t>Als groupIdentifier dient die Geplante-Abgabe-ID (früher eMED-ID), 
-die auch im e-Rezept mitgeführt wird. Werden von einem:r Arzt:Ärtztin mehrere Arzneimittel gleichzeitig verordnet, 
+    <t>Als groupIdentifier dient die eMED-ID, die auch im e-Rezept mitgeführt wird. 
+Werden von einem:r Arzt:Ärtztin mehrere Arzneimittel gleichzeitig verordnet, 
 wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
   </si>
   <si>
@@ -1388,7 +1385,7 @@
 </t>
   </si>
   <si>
-    <t>Angabe der Dosierinformationen strukturiert oder als Freitext. TODO: Inhalte AtEmedDosage fachlich prüfen.</t>
+    <t>Angabe der Dosierinformationen. TODO: Dosiervarianten.</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -1746,7 +1743,7 @@
     <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht.
 Erläutert die Absicht des verschreibenden Arztes. Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden. 
 Die Dokumentation über eine tatsächlich erfolgte Substitution erfolgt in der Dispense-Resource. 
-TODO: Eher keine Verwendung in der geplanten Abgabe.</t>
+TODO: Verwendung in der geplanten Abgabe prüfen.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:00:19+00:00</t>
+    <t>2026-03-10T11:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$73</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3018" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="534">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:31:06+00:00</t>
+    <t>2026-03-16T16:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -89,7 +89,6 @@
   <si>
     <t>Bildet eine geplante Abgabe eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
 Sie enthält das verordnete Arzneimittel und dessen Dosierung und spielgelt die Inhalte des e-Rezepts wider. Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation.
-Als groupIdentifier dient die Geplante-Abgabe-ID, die auch im e-Rezept mitgeführt wird.
 Werden mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer'). Verwendet R5 Backport Extensions.</t>
   </si>
   <si>
@@ -429,64 +428,10 @@
     <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>MedicationRequest.contained:medication</t>
-  </si>
-  <si>
-    <t>medication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medication {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication}
-</t>
-  </si>
-  <si>
-    <t>Definition of a Medication</t>
-  </si>
-  <si>
-    <t>This resource is primarily used for the identification and definition of a medication for the purposes of prescribing, dispensing, and administering a medication as well as for making statements about medication use.</t>
-  </si>
-  <si>
-    <t>NewRx/MedicationPrescribed--or--RxFill/MedicationDispensed--or--RxHistoryResponse/MedicationDispensed--or--RxHistoryResponse/MedicationPrescribed</t>
-  </si>
-  <si>
-    <t>ManufacturedProduct[classCode=ADMM]</t>
-  </si>
-  <si>
-    <t>MedicationRequest.contained:substance</t>
-  </si>
-  <si>
-    <t>substance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Substance {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-substance}
-</t>
-  </si>
-  <si>
-    <t>A homogeneous material with a definite composition</t>
-  </si>
-  <si>
-    <t>A homogeneous material with a definite composition.</t>
-  </si>
-  <si>
-    <t>Material</t>
   </si>
   <si>
     <t>MedicationRequest.extension</t>
@@ -506,6 +451,9 @@
 </t>
   </si>
   <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -549,22 +497,6 @@
     <t>Optional Extension Element - found in all resources.</t>
   </si>
   <si>
-    <t>MedicationRequest.extension:offLabelUse</t>
-  </si>
-  <si>
-    <t>offLabelUse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://profiles.ihe.net/PHARM/MPD/StructureDefinition/ihe-ext-offLabel}
-</t>
-  </si>
-  <si>
-    <t>Weist darauf hin, dass der verschreibende Arzt das Medikament wissentlich für eine Indikation, Altersgruppe, Dosierung oder Verabreichungsform verschrieben hat, die nicht von den Aufsichtsbehörden zugelassen ist und in der Verschreibungsinformation für das Produkt nicht erwähnt wird.</t>
-  </si>
-  <si>
-    <t>Indicates that the prescriber has intentionally prescribed the medication in a manner not covered by the product authorization — such as for a different indication, age group, dosage, or route of administration.</t>
-  </si>
-  <si>
     <t>MedicationRequest.modifierExtension</t>
   </si>
   <si>
@@ -595,7 +527,7 @@
 </t>
   </si>
   <si>
-    <t>Gepante-Abgabe-ID ? Verwendung prüfen.</t>
+    <t>Gepante-Abgabe-ID. TODO: Verwendung noch zu prüfen, evtl. basedon mit logischem Identifier ausreichend.</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -622,8 +554,12 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status der geplanten Abgabe (im Standardfall active oder complete): 
- (req) active | on-hold | cancelled | completed | entered-in-error | stopped  (entfernt: draft | unknown); TODO: Fachlich zu prüfen.</t>
+    <t>Status der geplanten Abgabe. 
+"active": bei Erstellung &lt;br&gt;
+"completed": implizit mittels Custom Operation gesetzt, nachdem alle Abgaben durchgeführt wurden (Rezept komplett eingelöst) (TODO: prüfen) &lt;br&gt;
+"entered-in-error": nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine Abgabe durchgeführt wurde &lt;br&gt;
+"stopped": TODO: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden) &lt;br&gt;
+(nicht verwendet: on-hold, stopped, cancelled, draft, unknown)</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -719,13 +655,45 @@
     <t>MedicationRequest.category</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Type of medication usage</t>
+  </si>
+  <si>
+    <t>Indicates the type of medication request (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
+  </si>
+  <si>
+    <t>The category can be used to include where the medication is expected to be consumed or other types of requests.</t>
+  </si>
+  <si>
+    <t>A coded concept identifying the category of medication request.  For example, where the medication is to be consumed or administered, or the type of medication treatment.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-category|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:coding.code}
+</t>
+  </si>
+  <si>
+    <t>Message/Body/NewRx/MedicationPrescribed/Directions++or ++Message/Body/NewRx/MedicationPrescribed/StructuredSIG</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
+  </si>
+  <si>
+    <t>MedicationRequest.category:mrcategory</t>
+  </si>
+  <si>
+    <t>mrcategory</t>
+  </si>
+  <si>
     <t>Kategorie zur Unterscheidung eines Medikationsplaneintrags von einer geplanten Abgabe (beide haben intent order)</t>
-  </si>
-  <si>
-    <t>Indicates the type of medication request (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
-  </si>
-  <si>
-    <t>The category can be used to include where the medication is expected to be consumed or other types of requests.</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -737,26 +705,22 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>A coded concept identifying the category of medication request.  For example, where the medication is to be consumed or administered, or the type of medication treatment.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-category|4.0.1</t>
-  </si>
-  <si>
-    <t>Message/Body/NewRx/MedicationPrescribed/Directions--or --Message/Body/NewRx/MedicationPrescribed/StructuredSIG</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
+    <t>MedicationRequest.category:recipetype</t>
+  </si>
+  <si>
+    <t>recipetype</t>
+  </si>
+  <si>
+    <t>Kategorie zur Unterscheidung, ob ein Kassen- oder Privatrezept erstellt wurde</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedicationRequestCategoryRecipeTypeVS</t>
   </si>
   <si>
     <t>MedicationRequest.priority</t>
   </si>
   <si>
-    <t>Priorität der geplanten Abgabe: routine | urgent | asap | stat. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Priorität der geplanten Abgabe. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates how quickly the Medication Request should be addressed with respect to other requests.</t>
@@ -815,26 +779,18 @@
     <t>MedicationRequest.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Medication|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
-    <t>Medication to be taken</t>
+    <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit 
+Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
   </si>
   <si>
     <t>Identifies the medication being requested. This is a link to a resource that represents the medication which may be the details of the medication or simply an attribute carrying a code that identifies the medication from a known list of medications.</t>
   </si>
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the Medication resource is recommended.  For example, if you require form or lot number or if the medication is compounded or extemporaneously prepared, then you must reference the Medication resource.</t>
-  </si>
-  <si>
-    <t>A coded concept identifying substance or product that can be ordered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
-  </si>
-  <si>
-    <t>closed</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -858,156 +814,6 @@
     <t>RXE-2-Give Code / RXO-1-Requested Give Code / RXC-2-Component Code</t>
   </si>
   <si>
-    <t>MedicationRequest.medication[x]:medicationReference</t>
-  </si>
-  <si>
-    <t>medicationReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-medication)
-</t>
-  </si>
-  <si>
-    <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit 
-Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationReference.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationReference.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationReference.reference</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-1
-</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-contained-ref:Medication must be contained (#...) {$this.startsWith('#')}</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationReference.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient")</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationReference.identifier</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x]:medicationReference.display</t>
-  </si>
-  <si>
-    <t>MedicationRequest.medication[x].display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
-  </si>
-  <si>
     <t>MedicationRequest.subject</t>
   </si>
   <si>
@@ -1126,7 +932,8 @@
   </si>
   <si>
     <t>Der Arzt oder die Ärztin, die die geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist 
-(eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen)</t>
+(eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen).
+TODO: Prüfen, der Rollen (HL7ATCorePractitioner nicht ausreichend).</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -1185,6 +992,9 @@
 </t>
   </si>
   <si>
+    <t>Keine Verwendung in der geplanten Abgabe. TODO: Abstimmung der Verwendung mit e-Diagnose.</t>
+  </si>
+  <si>
     <t>The person who entered the order on behalf of another individual for example in the case of a verbal or a telephone order.</t>
   </si>
   <si>
@@ -1197,8 +1007,7 @@
     <t>MedicationRequest.reasonCode</t>
   </si>
   <si>
-    <t>Grund für die Verordnung des Arzneimittels. 
-Entweder Code oder Referenz (TODO: Evtl. Invariante). Verwendung in geplanter Abgabe prüfen.</t>
+    <t>Grund für die Verordnung des Arzneimittels als Code oder Referenz. Derzeit keine Verwendung in geplanter Abgabe.</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -1287,7 +1096,9 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf den zugrundeliegenden Medikationsplaneintrag, auf dem diese geplante Abgabe basiert.</t>
+    <t>Referenz auf die (aktuelle) Version des zugrundeliegenden Medikationsplaneintrags, auf dem diese geplante Abgabe basiert.
+TODO: zu prüfen: zusätzliche logische Referenz: reference.identifier 
+{Medikationsplaneintrag-ID}_{Medikationsplaneintrag-ID_Version}.</t>
   </si>
   <si>
     <t>A plan or request that is fulfilled in whole or in part by this medication request.</t>
@@ -1304,7 +1115,8 @@
   <si>
     <t>Als groupIdentifier dient die eMED-ID, die auch im e-Rezept mitgeführt wird. 
 Werden von einem:r Arzt:Ärtztin mehrere Arzneimittel gleichzeitig verordnet, 
-wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
+wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').
+TODO: eMED-ID Wording ist evtl. aufgrund des Parallelbetriebs noch anzupassen</t>
   </si>
   <si>
     <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition or prescription.</t>
@@ -1363,7 +1175,8 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen zur geplanten Abgabe. TODO: prüfen</t>
+    <t>Zusätzliche Informationen zur geplanten Abgabe (Kommunikations zw. Arzt und Apotheke); die nicht die Dosierung betreffen. 
+TODO: prüfen was CDA derzeit zulässt; HL7 Consultation, ob Feld benötigt</t>
   </si>
   <si>
     <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
@@ -1407,7 +1220,7 @@
 </t>
   </si>
   <si>
-    <t>Details zur geplanten Abgabe des Arzneimittels. TODO: alle Elemente fachlich zu prüfen.</t>
+    <t>Details zur geplanten Abgabe des Arzneimittels.</t>
   </si>
   <si>
     <t>Indicates the specific details for the dispense or medication supply part of a medication request (also known as a Medication Prescription or Medication Order).  Note that this information is not always sent with the order.  There may be in some settings (e.g. hospitals) institutional or system support for completing the dispense details in the pharmacy department.</t>
@@ -1422,7 +1235,32 @@
     <t>MedicationRequest.dispenseRequest.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>MedicationRequest.dispenseRequest.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.modifierExtension</t>
@@ -1473,7 +1311,7 @@
 </t>
   </si>
   <si>
-    <t>Anzahl der Einheiten für die erste Abgabe, z.B. 30 Kapseln oder 100 mg.</t>
+    <t>Anzahl der Einheiten für die erste Abgabe, z.B. 30 Kapseln oder 100 mg. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The amount or quantity to provide as part of the first dispense.</t>
@@ -1501,7 +1339,7 @@
     <t>MedicationRequest.dispenseRequest.dispenseInterval</t>
   </si>
   <si>
-    <t>Mindestzeitraum zwischen den Abgaben.</t>
+    <t>Mindestzeitraum zwischen den Abgaben. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The minimum period of time that must occur between dispenses of the medication.</t>
@@ -1514,7 +1352,11 @@
 </t>
   </si>
   <si>
-    <t>Zeitraum in dem die geplante Abgabe eingelöst werden kann.</t>
+    <t>Zeitraum in dem die geplante Abgabe eingelöst werden kann. Teilabgaben verlängern die Einlösedauer.
+Falls das start-Datum dem authoredOn-Datum entspricht, kann die Angabe entfallen. 
+Der Gültigkeitszeitraum ist abhängig von der Rezeptart. 
+TODO: Evtl. automatische Berechnung des Gültigkeitszeitraums.
+TODO: Fachlich zu klären, ob die Gültigkeitsdauer eingeschränkt werden darf.</t>
   </si>
   <si>
     <t>This indicates the validity period of a prescription (stale dating the Prescription).</t>
@@ -1539,7 +1381,7 @@
 </t>
   </si>
   <si>
-    <t>Anzahl der weiteren möglichen Einlösungen.</t>
+    <t>Anzahl der weiteren möglichen Einlösungen. TODO: Invariante: Verpflichtende Eingabe, wenn Privatrezept.</t>
   </si>
   <si>
     <t>An integer indicating the number of times, in addition to the original dispense, (aka refills or repeats) that the patient can receive the prescribed medication. Usage Notes: This integer does not include the original order dispense. This means that if an order indicates dispense 30 tablets plus "3 repeats", then the order can be dispensed a total of 4 times and the patient can receive a total of 120 tablets.  A prescriber may explicitly say that zero refills are permitted after the initial dispense.</t>
@@ -1560,7 +1402,8 @@
     <t>MedicationRequest.dispenseRequest.quantity</t>
   </si>
   <si>
-    <t>Menge des Medikaments, die bei jeder Abgabe bereitgestellt werden soll, z.B. 30 Stück.</t>
+    <t>Menge des Medikaments, die bei jeder Abgabe bereitgestellt werden soll. 
+Im Fall einer Medikation mit PZN: z.B. 2 Packungen (OP2), im Fall einer Magistralen Anwendung: 1.</t>
   </si>
   <si>
     <t>The amount that is to be dispensed for one fill.</t>
@@ -1597,6 +1440,9 @@
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.value</t>
@@ -1606,7 +1452,7 @@
 </t>
   </si>
   <si>
-    <t>Dauer, für die die bereitgestellte Menge des Medikaments voraussichtlich ausreicht, z.B. 30 Tage.</t>
+    <t>Dauer, für die die bereitgestellte Menge des Medikaments voraussichtlich ausreicht, z.B. 30 Tage. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
@@ -1741,9 +1587,7 @@
   </si>
   <si>
     <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht.
-Erläutert die Absicht des verschreibenden Arztes. Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden. 
-Die Dokumentation über eine tatsächlich erfolgte Substitution erfolgt in der Dispense-Resource. 
-TODO: Verwendung in der geplanten Abgabe prüfen.</t>
+Erläutert die Absicht des verschreibenden Arztes. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -1823,7 +1667,7 @@
 </t>
   </si>
   <si>
-    <t>Im Falle einer Änderung wird auf die ersetzte geplante Abgabe verwiesen.</t>
+    <t>Im Falle einer Änderung wird auf die ersetzte geplante Abgabe verwiesen. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>A link to a resource representing an earlier order related order or prescription.</t>
@@ -1846,7 +1690,8 @@
 </t>
   </si>
   <si>
-    <t>Klinisches Problem mit Maßnahme. Nur mittesl Referenz auf Ressouce DetectedIssue. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Klinisches Problem mit Maßnahme, mittels Referenz auf Ressouce DetectedIssue. Keine Verwendung in der geplanten 
+Abgabe.</t>
   </si>
   <si>
     <t>Indicates an actual or potential clinical issue with or between one or more active or proposed clinical actions for a patient; e.g. Drug-drug interaction, duplicate therapy, dosage alert etc.</t>
@@ -1865,7 +1710,8 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf Provenance-Ressourcen, die verschiedene relevante Versionen dieser Ressource dokumentieren. 
+    <t>Referenz auf Provenance-Ressourcen, die 
+verschiedene relevante Versionen dieser Ressource dokumentieren. 
 Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
@@ -2203,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO81"/>
+  <dimension ref="A1:AO73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
@@ -2231,7 +2077,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="138.53125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -3084,7 +2930,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>81</v>
@@ -3146,17 +2992,19 @@
         <v>21</v>
       </c>
       <c r="AB8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF8" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="AC8" s="2"/>
-      <c r="AD8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -3177,7 +3025,7 @@
         <v>21</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>21</v>
@@ -3188,23 +3036,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>137</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -3216,17 +3062,15 @@
         <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>131</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -3263,19 +3107,17 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -3287,16 +3129,16 @@
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>142</v>
+        <v>21</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>21</v>
@@ -3307,13 +3149,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C10" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>21</v>
@@ -3323,7 +3165,7 @@
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
@@ -3335,17 +3177,15 @@
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>131</v>
-      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
@@ -3394,7 +3234,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3403,10 +3243,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>21</v>
+        <v>141</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -3415,7 +3255,7 @@
         <v>21</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>21</v>
@@ -3426,12 +3266,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="B11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
@@ -3440,7 +3282,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -3497,17 +3339,19 @@
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AC11" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3516,10 +3360,10 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>21</v>
@@ -3528,7 +3372,7 @@
         <v>21</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>21</v>
@@ -3539,44 +3383,46 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>21</v>
       </c>
@@ -3624,7 +3470,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3633,10 +3479,10 @@
         <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>21</v>
@@ -3645,7 +3491,7 @@
         <v>21</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>21</v>
@@ -3656,14 +3502,12 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>21</v>
       </c>
@@ -3672,7 +3516,7 @@
         <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
@@ -3684,15 +3528,17 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
@@ -3741,7 +3587,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3750,66 +3596,66 @@
         <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>172</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>173</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3834,13 +3680,11 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3858,31 +3702,31 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>21</v>
+        <v>176</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>21</v>
+        <v>177</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>21</v>
@@ -3890,46 +3734,44 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
       </c>
@@ -3953,13 +3795,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>21</v>
+        <v>187</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3977,28 +3819,28 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>21</v>
@@ -4009,10 +3851,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4023,28 +3865,28 @@
         <v>90</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>91</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4055,7 +3897,7 @@
         <v>21</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>21</v>
@@ -4070,13 +3912,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>21</v>
+        <v>196</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -4094,13 +3936,13 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>21</v>
@@ -4109,27 +3951,27 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4137,31 +3979,31 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>90</v>
+        <v>201</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>110</v>
+        <v>181</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4187,35 +4029,35 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y17" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="Z17" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
@@ -4224,41 +4066,43 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>195</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>21</v>
@@ -4267,16 +4111,16 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4287,7 +4131,7 @@
         <v>21</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>21</v>
@@ -4302,7 +4146,7 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="Y18" t="s" s="2">
         <v>205</v>
@@ -4326,13 +4170,13 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
@@ -4341,16 +4185,16 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>21</v>
@@ -4358,12 +4202,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>21</v>
       </c>
@@ -4378,22 +4224,22 @@
         <v>91</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>110</v>
+        <v>181</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4404,7 +4250,7 @@
         <v>21</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>21</v>
@@ -4419,13 +4265,11 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -4443,13 +4287,13 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
@@ -4458,27 +4302,27 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>216</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AN19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" hidden="true">
+      <c r="A20" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AO19" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>219</v>
-      </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4486,32 +4330,30 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K20" t="s" s="2">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>222</v>
-      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -4521,7 +4363,7 @@
         <v>21</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>21</v>
@@ -4536,13 +4378,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -4560,13 +4402,13 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>21</v>
@@ -4575,16 +4417,16 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>21</v>
+        <v>223</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>21</v>
@@ -4592,10 +4434,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4612,21 +4454,23 @@
         <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4651,13 +4495,13 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>231</v>
+        <v>21</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>232</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
@@ -4675,7 +4519,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4690,16 +4534,16 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>21</v>
@@ -4707,10 +4551,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4727,23 +4571,21 @@
         <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4792,7 +4634,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4813,7 +4655,7 @@
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -4822,12 +4664,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4835,13 +4677,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
@@ -4850,15 +4692,17 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -4907,10 +4751,10 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>90</v>
@@ -4922,22 +4766,22 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AN23" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>21</v>
-      </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>247</v>
       </c>
@@ -5000,26 +4844,28 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AC24" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>254</v>
+        <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>247</v>
@@ -5037,61 +4883,59 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AM24" t="s" s="2">
+    </row>
+    <row r="25" hidden="true">
+      <c r="A25" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AN24" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>260</v>
-      </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5141,10 +4985,10 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>90</v>
@@ -5156,27 +5000,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>256</v>
+        <v>177</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5187,7 +5031,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -5199,13 +5043,13 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5256,75 +5100,73 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>21</v>
+        <v>270</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>272</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>150</v>
+        <v>273</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -5361,54 +5203,54 @@
         <v>21</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AG27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AL27" t="s" s="2">
-        <v>21</v>
+        <v>277</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>21</v>
+        <v>279</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>21</v>
+        <v>280</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5416,13 +5258,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
@@ -5431,17 +5273,15 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -5490,7 +5330,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5499,22 +5339,22 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>283</v>
+        <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>284</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>21</v>
+        <v>285</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>135</v>
+        <v>254</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>21</v>
@@ -5522,10 +5362,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5536,7 +5376,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -5545,20 +5385,18 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>104</v>
+        <v>288</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>287</v>
+        <v>234</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N29" t="s" s="2">
         <v>289</v>
       </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -5583,13 +5421,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>292</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -5607,7 +5445,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5622,16 +5460,16 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>21</v>
+        <v>290</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>135</v>
+        <v>291</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>21</v>
@@ -5639,10 +5477,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5653,7 +5491,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -5665,16 +5503,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>296</v>
+        <v>234</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5700,13 +5538,13 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>21</v>
+        <v>296</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>21</v>
+        <v>297</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5724,7 +5562,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5739,13 +5577,13 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>21</v>
+        <v>298</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
@@ -5756,10 +5594,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5770,7 +5608,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5779,20 +5617,18 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M31" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>305</v>
-      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5841,7 +5677,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5862,21 +5698,21 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>135</v>
+        <v>304</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>21</v>
+        <v>305</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5884,31 +5720,31 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5934,13 +5770,13 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>21</v>
+        <v>310</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>21</v>
+        <v>311</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5958,13 +5794,13 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
@@ -6004,7 +5840,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -6081,7 +5917,7 @@
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
@@ -6093,24 +5929,24 @@
         <v>322</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>323</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>325</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6130,16 +5966,16 @@
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6190,7 +6026,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6205,27 +6041,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>332</v>
-      </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6233,13 +6069,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -6248,13 +6084,13 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>333</v>
+        <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6305,13 +6141,13 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
@@ -6320,27 +6156,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>337</v>
+        <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>340</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6363,13 +6199,13 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6420,13 +6256,13 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
@@ -6435,27 +6271,27 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>346</v>
+        <v>21</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6463,31 +6299,33 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>348</v>
+        <v>161</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>244</v>
+        <v>340</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
       </c>
@@ -6535,7 +6373,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6550,16 +6388,16 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>352</v>
+        <v>21</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>21</v>
@@ -6567,10 +6405,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6590,19 +6428,19 @@
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>244</v>
+        <v>346</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6628,13 +6466,13 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6652,7 +6490,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6667,13 +6505,13 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6684,10 +6522,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6710,13 +6548,13 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6767,13 +6605,13 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6782,27 +6620,27 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>21</v>
+        <v>355</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6813,10 +6651,10 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -6825,17 +6663,15 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>200</v>
+        <v>358</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6860,13 +6696,13 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>370</v>
+        <v>21</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -6884,7 +6720,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6899,27 +6735,27 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>375</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6930,7 +6766,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6942,16 +6778,16 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7001,7 +6837,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7016,27 +6852,27 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7044,28 +6880,28 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7116,13 +6952,13 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
@@ -7131,13 +6967,13 @@
         <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>387</v>
+        <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -7148,10 +6984,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7162,7 +6998,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
@@ -7171,16 +7007,16 @@
         <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>104</v>
+        <v>378</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7231,19 +7067,19 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>21</v>
@@ -7252,7 +7088,7 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7261,43 +7097,45 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>393</v>
+        <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -7346,7 +7184,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7358,16 +7196,16 @@
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>396</v>
+        <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7376,45 +7214,47 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I45" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O45" t="s" s="2">
-        <v>401</v>
+        <v>158</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7463,28 +7303,28 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>402</v>
+        <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>403</v>
+        <v>133</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7495,10 +7335,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7521,16 +7361,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>200</v>
+        <v>372</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7556,13 +7396,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>204</v>
+        <v>21</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>408</v>
+        <v>21</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>409</v>
+        <v>21</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -7580,7 +7420,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7601,7 +7441,7 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7612,10 +7452,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7626,7 +7466,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>21</v>
@@ -7638,13 +7478,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>412</v>
+        <v>378</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>244</v>
+        <v>379</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>413</v>
+        <v>380</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7695,28 +7535,28 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>414</v>
+        <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7725,16 +7565,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7744,7 +7584,7 @@
         <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
@@ -7753,15 +7593,17 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>417</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>418</v>
+        <v>384</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7810,7 +7652,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>416</v>
+        <v>386</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7822,16 +7664,16 @@
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>420</v>
+        <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>421</v>
+        <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>422</v>
+        <v>382</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7840,46 +7682,48 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I49" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I49" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J49" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>424</v>
+        <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>425</v>
+        <v>389</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>426</v>
+        <v>390</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7927,7 +7771,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>423</v>
+        <v>391</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7939,16 +7783,16 @@
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>428</v>
+        <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>429</v>
+        <v>133</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7957,12 +7801,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7976,7 +7820,7 @@
         <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -7985,13 +7829,13 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>432</v>
+        <v>402</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>433</v>
+        <v>403</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8042,7 +7886,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8060,10 +7904,10 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>434</v>
+        <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>435</v>
+        <v>404</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -8074,10 +7918,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>436</v>
+        <v>405</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>436</v>
+        <v>405</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8100,13 +7944,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>266</v>
+        <v>406</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>267</v>
+        <v>407</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>268</v>
+        <v>408</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8157,7 +8001,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>269</v>
+        <v>405</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8169,7 +8013,7 @@
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
@@ -8178,7 +8022,7 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>270</v>
+        <v>409</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8189,21 +8033,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -8215,17 +8059,15 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>150</v>
+        <v>406</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>273</v>
+        <v>411</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8274,19 +8116,19 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>276</v>
+        <v>410</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -8295,7 +8137,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>270</v>
+        <v>409</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8304,47 +8146,47 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>439</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>150</v>
+        <v>414</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>440</v>
+        <v>415</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>441</v>
+        <v>416</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>176</v>
+        <v>417</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>177</v>
+        <v>418</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8393,28 +8235,28 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>442</v>
+        <v>413</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>135</v>
+        <v>420</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8425,10 +8267,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8451,16 +8293,16 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>444</v>
+        <v>423</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>445</v>
+        <v>424</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8510,7 +8352,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8528,24 +8370,24 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>21</v>
+        <v>428</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8553,13 +8395,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>21</v>
@@ -8568,13 +8410,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>266</v>
+        <v>401</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>267</v>
+        <v>430</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>268</v>
+        <v>431</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8625,7 +8467,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>269</v>
+        <v>429</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8637,41 +8479,41 @@
         <v>21</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>21</v>
+        <v>432</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>270</v>
+        <v>433</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>21</v>
+        <v>434</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -8683,16 +8525,16 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>150</v>
+        <v>406</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>273</v>
+        <v>436</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>274</v>
+        <v>437</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>176</v>
+        <v>438</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8742,28 +8584,28 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>276</v>
+        <v>435</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>270</v>
+        <v>440</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8774,46 +8616,42 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>439</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>150</v>
+        <v>378</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>440</v>
+        <v>379</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8861,19 +8699,19 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>442</v>
+        <v>381</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
@@ -8882,7 +8720,7 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>135</v>
+        <v>382</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8893,21 +8731,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
@@ -8919,15 +8757,17 @@
         <v>21</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>452</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>453</v>
+        <v>384</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>21</v>
@@ -8964,31 +8804,31 @@
         <v>21</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>21</v>
+        <v>443</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>21</v>
+        <v>139</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>451</v>
+        <v>386</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
@@ -8997,7 +8837,7 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>455</v>
+        <v>382</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -9008,10 +8848,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9031,19 +8871,23 @@
         <v>21</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
       </c>
@@ -9091,7 +8935,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9112,21 +8956,21 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>21</v>
+        <v>452</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9140,29 +8984,33 @@
         <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I60" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I60" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J60" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q60" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="L60" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
         <v>21</v>
       </c>
@@ -9182,13 +9030,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>21</v>
+        <v>458</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>21</v>
+        <v>459</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9206,7 +9054,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9227,21 +9075,21 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>21</v>
+        <v>462</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9255,28 +9103,26 @@
         <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K61" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="N61" s="2"/>
+      <c r="O61" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9325,7 +9171,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9343,24 +9189,24 @@
         <v>21</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AM61" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>472</v>
-      </c>
       <c r="B62" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9374,27 +9220,27 @@
         <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K62" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="L62" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9442,7 +9288,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9451,7 +9297,7 @@
         <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>21</v>
+        <v>475</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>102</v>
@@ -9460,24 +9306,24 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="AM62" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>480</v>
-      </c>
       <c r="B63" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9491,25 +9337,29 @@
         <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K63" t="s" s="2">
-        <v>452</v>
+        <v>110</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O63" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
       </c>
@@ -9557,7 +9407,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9575,24 +9425,24 @@
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="AN63" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>486</v>
-      </c>
       <c r="B64" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9603,10 +9453,10 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>21</v>
@@ -9615,17 +9465,15 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M64" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>489</v>
-      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -9674,7 +9522,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9692,13 +9540,13 @@
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>21</v>
+        <v>305</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>21</v>
@@ -9706,10 +9554,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9720,7 +9568,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
@@ -9732,13 +9580,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>266</v>
+        <v>372</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>267</v>
+        <v>490</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>268</v>
+        <v>491</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9789,7 +9637,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>269</v>
+        <v>489</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9801,16 +9649,16 @@
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>21</v>
+        <v>492</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>270</v>
+        <v>493</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9821,21 +9669,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>21</v>
@@ -9847,17 +9695,15 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>150</v>
+        <v>378</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>273</v>
+        <v>379</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9894,31 +9740,31 @@
         <v>21</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>275</v>
+        <v>21</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
@@ -9927,7 +9773,7 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>270</v>
+        <v>382</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9938,21 +9784,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -9961,23 +9807,21 @@
         <v>21</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>495</v>
+        <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>496</v>
+        <v>384</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>497</v>
+        <v>385</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>21</v>
       </c>
@@ -10025,19 +9869,19 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>500</v>
+        <v>386</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>21</v>
@@ -10046,32 +9890,32 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>501</v>
+        <v>382</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>502</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>21</v>
+        <v>388</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>21</v>
@@ -10083,24 +9927,24 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>504</v>
+        <v>389</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O68" t="s" s="2">
-        <v>506</v>
+        <v>158</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q68" t="s" s="2">
-        <v>507</v>
-      </c>
+      <c r="Q68" s="2"/>
       <c r="R68" t="s" s="2">
         <v>21</v>
       </c>
@@ -10120,13 +9964,13 @@
         <v>21</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>508</v>
+        <v>21</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>509</v>
+        <v>21</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>21</v>
@@ -10144,19 +9988,19 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>510</v>
+        <v>391</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>21</v>
@@ -10165,21 +10009,21 @@
         <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>511</v>
+        <v>133</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>512</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10187,7 +10031,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>90</v>
@@ -10199,21 +10043,21 @@
         <v>21</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>266</v>
+        <v>498</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>21</v>
       </c>
@@ -10237,13 +10081,13 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>21</v>
+        <v>502</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>21</v>
+        <v>503</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -10261,10 +10105,10 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>90</v>
@@ -10279,24 +10123,24 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>21</v>
+        <v>492</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>519</v>
+        <v>505</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10316,21 +10160,19 @@
         <v>21</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>104</v>
+        <v>181</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>523</v>
-      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -10354,13 +10196,13 @@
         <v>21</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>21</v>
+        <v>509</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>21</v>
+        <v>510</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -10378,7 +10220,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10387,7 +10229,7 @@
         <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>525</v>
+        <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>102</v>
@@ -10396,24 +10238,24 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>21</v>
+        <v>511</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10424,7 +10266,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>21</v>
@@ -10433,23 +10275,19 @@
         <v>21</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>110</v>
+        <v>515</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>531</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>21</v>
       </c>
@@ -10497,7 +10335,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10512,31 +10350,31 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>21</v>
+        <v>518</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>21</v>
+        <v>511</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>519</v>
+        <v>21</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>21</v>
+        <v>521</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10555,15 +10393,17 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>21</v>
@@ -10612,13 +10452,13 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>21</v>
@@ -10633,21 +10473,21 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10658,10 +10498,10 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>21</v>
@@ -10670,15 +10510,17 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>431</v>
+        <v>528</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>531</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>21</v>
@@ -10727,13 +10569,13 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>21</v>
@@ -10742,955 +10584,23 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>21</v>
+        <v>532</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>542</v>
+        <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO81" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO81">
+  <autoFilter ref="A1:AO73">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11700,7 +10610,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI80">
+  <conditionalFormatting sqref="A2:AI72">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T16:50:24+00:00</t>
+    <t>2026-03-19T16:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -555,9 +555,9 @@
   </si>
   <si>
     <t>Status der geplanten Abgabe. 
-"active": bei Erstellung &lt;br&gt;
-"completed": implizit mittels Custom Operation gesetzt, nachdem alle Abgaben durchgeführt wurden (Rezept komplett eingelöst) (TODO: prüfen) &lt;br&gt;
-"entered-in-error": nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine Abgabe durchgeführt wurde &lt;br&gt;
+"active": offne, geplante Abgabe &lt;br&gt;
+"completed": implizit mittels Custom Operation gesetzt, nachdem alle Abgaben durchgeführt wurden (Rezept komplett eingelöst) (TODO: techn. prüfen) &lt;br&gt;
+"entered-in-error": nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde (TODO: techn. prüfen?) &lt;br&gt;
 "stopped": TODO: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden) &lt;br&gt;
 (nicht verwendet: on-hold, stopped, cancelled, draft, unknown)</t>
   </si>
@@ -711,10 +711,10 @@
     <t>recipetype</t>
   </si>
   <si>
-    <t>Kategorie zur Unterscheidung, ob ein Kassen- oder Privatrezept erstellt wurde</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedicationRequestCategoryRecipeTypeVS</t>
+    <t>Kategorie zur Unterscheidung, ob ein Kassen-, Privat- oder Substitutionsrezept erstellt wurde.</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet/elga-medikationrezeptart</t>
   </si>
   <si>
     <t>MedicationRequest.priority</t>
@@ -933,7 +933,7 @@
   <si>
     <t>Der Arzt oder die Ärztin, die die geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist 
 (eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen).
-TODO: Prüfen, der Rollen (HL7ATCorePractitioner nicht ausreichend).</t>
+TODO: HL7ATCore-Practitioner-Profile profilieren.</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -992,7 +992,7 @@
 </t>
   </si>
   <si>
-    <t>Keine Verwendung in der geplanten Abgabe. TODO: Abstimmung der Verwendung mit e-Diagnose.</t>
+    <t>Person der Dateineingabe. Gemäß Vorgaben im CDA keine Verwendung in der geplanten Abgabe. TODO: Abstimmung der Verwendung mit e-Diagnose.</t>
   </si>
   <si>
     <t>The person who entered the order on behalf of another individual for example in the case of a verbal or a telephone order.</t>
@@ -1007,7 +1007,7 @@
     <t>MedicationRequest.reasonCode</t>
   </si>
   <si>
-    <t>Grund für die Verordnung des Arzneimittels als Code oder Referenz. Derzeit keine Verwendung in geplanter Abgabe.</t>
+    <t xml:space="preserve">Grund für die Verordnung des Arzneimittels als Code oder Referenz. Bis zur Verfügbarkeit von e-Diagnose keine Verwendung in geplanter Abgabe. </t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -1352,11 +1352,15 @@
 </t>
   </si>
   <si>
-    <t>Zeitraum in dem die geplante Abgabe eingelöst werden kann. Teilabgaben verlängern die Einlösedauer.
-Falls das start-Datum dem authoredOn-Datum entspricht, kann die Angabe entfallen. 
-Der Gültigkeitszeitraum ist abhängig von der Rezeptart. 
-TODO: Evtl. automatische Berechnung des Gültigkeitszeitraums.
-TODO: Fachlich zu klären, ob die Gültigkeitsdauer eingeschränkt werden darf.</t>
+    <t xml:space="preserve">Zeitraum in dem die geplante Abgabe eingelöst werden kann. &lt;br&gt;
+Der Gültigkeitszeitraum ist abhängig von der Rezeptart (gemäß e-Med v2): &lt;/br&gt;
+Kassenrezept: ab Erstelldatum einen Monat gültig (vom Ausstellungszeitpunkt bis zum gleichen Tag des Folgemonats 23:59 Uhr); validityPeriod.start kein Datum in der Zukunft; bei einer Teilabgabe verlängert sich die gesamte Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess).&lt;br&gt;
+Privatrezept: ab Erstelldatum maximal 365 Tage gültig, wenn die erste Einlösung innerhalb von 1 Monat ab Erstelldatum erfolgt (sonst Status abgelaufen). validityPeriod.start kein Datum in der Zukunft; Die Gültigkeitsdauer (validityPeriod.end) kann vom Arzt definiert werden.&lt;br&gt;
+Substitutionsrezept: Maximale Gültigkeitsdauer 12 Monate. Das validityPeriod.start darf maximal einen Monat in der Zukunft liegen, gültig bis das validityPeriod.end erreicht ist.&lt;br&gt;
+Falls das start-Datum dem authoredOn-Datum entspricht, kann das start-Datum entfallen.&lt;br&gt;&lt;br&gt;
+TODO: Techn. Prüfung der Gültigkeitszeiträume&lt;br&gt;
+zu prüfen: Kann beim Kassenrezept validityPeriod.start in der Vergangenheit liegen, wenn geplante Abgabe in nachhinein erstellt wurde (z.B. wenn Arzt auf Urlaub und eine Notfallabgabe in der Apotheke durchgeführt wurde)?&lt;br&gt;
+</t>
   </si>
   <si>
     <t>This indicates the validity period of a prescription (stale dating the Prescription).</t>
@@ -1381,7 +1385,12 @@
 </t>
   </si>
   <si>
-    <t>Anzahl der weiteren möglichen Einlösungen. TODO: Invariante: Verpflichtende Eingabe, wenn Privatrezept.</t>
+    <t xml:space="preserve">Anzahl der weiteren möglichen Einlösungen:&lt;br&gt;
+Kassenrezept: keine weitere Einlösung möglich (fixer Wert 0) &lt;br&gt;
+Privatrezept: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden&lt;br&gt;
+Sustitutionsrzepet: keine weitere Einlösung möglich (fixer Wert 0) &lt;br&gt;&lt;br&gt;
+TODO: Techn. Prüfung: Wenn Kassenrezept oder Substitutionsrezept, dann 0. Verpflichtende Eingabe, wenn Privatrezept, max 6.&lt;br&gt;
+</t>
   </si>
   <si>
     <t>An integer indicating the number of times, in addition to the original dispense, (aka refills or repeats) that the patient can receive the prescribed medication. Usage Notes: This integer does not include the original order dispense. This means that if an order indicates dispense 30 tablets plus "3 repeats", then the order can be dispensed a total of 4 times and the patient can receive a total of 120 tablets.  A prescriber may explicitly say that zero refills are permitted after the initial dispense.</t>
@@ -1403,7 +1412,8 @@
   </si>
   <si>
     <t>Menge des Medikaments, die bei jeder Abgabe bereitgestellt werden soll. 
-Im Fall einer Medikation mit PZN: z.B. 2 Packungen (OP2), im Fall einer Magistralen Anwendung: 1.</t>
+Da sich die Angaben zum Arzneimittel jeweils auf eine Packung der Arznei beziehen, MUSS die Anzahl der auszugebenden Packungen angegeben werden (mindestens 1). 
+Dies gilt für Arzneimittel mit PZN und magistralen Zubereitungen, z.B. 2 Packungen (OP2), im Fall einer Magistralen Anwendung: Menge 1.</t>
   </si>
   <si>
     <t>The amount that is to be dispensed for one fill.</t>
@@ -2077,7 +2087,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="138.53125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -8278,7 +8288,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>90</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="535">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T16:44:44+00:00</t>
+    <t>2026-03-20T13:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -554,15 +554,15 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status der geplanten Abgabe. 
-"active": offne, geplante Abgabe &lt;br&gt;
-"completed": implizit mittels Custom Operation gesetzt, nachdem alle Abgaben durchgeführt wurden (Rezept komplett eingelöst) (TODO: techn. prüfen) &lt;br&gt;
-"entered-in-error": nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde (TODO: techn. prüfen?) &lt;br&gt;
-"stopped": TODO: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden) &lt;br&gt;
+    <t>Status der geplanten Abgabe: active | completed | entered-in-error | stopped. Details siehe Definition.</t>
+  </si>
+  <si>
+    <t>Status der geplanten Abgabe:
+* \"active\": offene, geplante Abgabe 
+* \"completed\": implizit mittels Custom Operation gesetzt, nachdem alle Abgaben durchgeführt wurden (Rezept komplett eingelöst) (TODO: techn. prüfen) 
+* \"entered-in-error\": nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde (TODO: techn. prüfen?) 
+* \"stopped\": TODO: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden)
 (nicht verwendet: on-hold, stopped, cancelled, draft, unknown)</t>
-  </si>
-  <si>
-    <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
@@ -1159,6 +1159,9 @@
 </t>
   </si>
   <si>
+    <t>Versicherungsinformatinen als Coverage oder ClaimResponse Resource. Keine Verwendung in der geplanten Abgabe.</t>
+  </si>
+  <si>
     <t>Insurance plans, coverage extensions, pre-authorizations and/or pre-determinations that may be required for delivering the requested service.</t>
   </si>
   <si>
@@ -1352,18 +1355,14 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Zeitraum in dem die geplante Abgabe eingelöst werden kann. &lt;br&gt;
-Der Gültigkeitszeitraum ist abhängig von der Rezeptart (gemäß e-Med v2): &lt;/br&gt;
-Kassenrezept: ab Erstelldatum einen Monat gültig (vom Ausstellungszeitpunkt bis zum gleichen Tag des Folgemonats 23:59 Uhr); validityPeriod.start kein Datum in der Zukunft; bei einer Teilabgabe verlängert sich die gesamte Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess).&lt;br&gt;
-Privatrezept: ab Erstelldatum maximal 365 Tage gültig, wenn die erste Einlösung innerhalb von 1 Monat ab Erstelldatum erfolgt (sonst Status abgelaufen). validityPeriod.start kein Datum in der Zukunft; Die Gültigkeitsdauer (validityPeriod.end) kann vom Arzt definiert werden.&lt;br&gt;
-Substitutionsrezept: Maximale Gültigkeitsdauer 12 Monate. Das validityPeriod.start darf maximal einen Monat in der Zukunft liegen, gültig bis das validityPeriod.end erreicht ist.&lt;br&gt;
-Falls das start-Datum dem authoredOn-Datum entspricht, kann das start-Datum entfallen.&lt;br&gt;&lt;br&gt;
-TODO: Techn. Prüfung der Gültigkeitszeiträume&lt;br&gt;
-zu prüfen: Kann beim Kassenrezept validityPeriod.start in der Vergangenheit liegen, wenn geplante Abgabe in nachhinein erstellt wurde (z.B. wenn Arzt auf Urlaub und eine Notfallabgabe in der Apotheke durchgeführt wurde)?&lt;br&gt;
-</t>
-  </si>
-  <si>
-    <t>This indicates the validity period of a prescription (stale dating the Prescription).</t>
+    <t>Die Anzahl der weiteren möglichen Einlösungen ist abhängig von der Rezeptart (siehe Definition).</t>
+  </si>
+  <si>
+    <t>Anzahl der weiteren möglichen Einlösungen:
+* **Kassenrezept**: keine weitere Einlösung möglich (fixer Wert 0)
+* **Privatrezept**: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden
+* **Sustitutionsrzepet**: keine weitere Einlösung möglich (fixer Wert 0) 
+TODO: Techn. Prüfung: Wenn Kassenrezept oder Substitutionsrezept, dann 0. Verpflichtende Eingabe, wenn Privatrezept, max 6.</t>
   </si>
   <si>
     <t>It reflects the prescribers' perspective for the validity of the prescription. Dispenses must not be made against the prescription outside of this period. The lower-bound of the Dispensing Window signifies the earliest date that the prescription can be filled for the first time. If an upper-bound is not specified then the Prescription is open-ended or will default to a stale-date based on regulations.</t>
@@ -1385,12 +1384,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Anzahl der weiteren möglichen Einlösungen:&lt;br&gt;
-Kassenrezept: keine weitere Einlösung möglich (fixer Wert 0) &lt;br&gt;
-Privatrezept: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden&lt;br&gt;
-Sustitutionsrzepet: keine weitere Einlösung möglich (fixer Wert 0) &lt;br&gt;&lt;br&gt;
-TODO: Techn. Prüfung: Wenn Kassenrezept oder Substitutionsrezept, dann 0. Verpflichtende Eingabe, wenn Privatrezept, max 6.&lt;br&gt;
-</t>
+    <t>Number of refills authorized</t>
   </si>
   <si>
     <t>An integer indicating the number of times, in addition to the original dispense, (aka refills or repeats) that the patient can receive the prescribed medication. Usage Notes: This integer does not include the original order dispense. This means that if an order indicates dispense 30 tablets plus "3 repeats", then the order can be dispensed a total of 4 times and the patient can receive a total of 120 tablets.  A prescriber may explicitly say that zero refills are permitted after the initial dispense.</t>
@@ -1413,7 +1407,7 @@
   <si>
     <t>Menge des Medikaments, die bei jeder Abgabe bereitgestellt werden soll. 
 Da sich die Angaben zum Arzneimittel jeweils auf eine Packung der Arznei beziehen, MUSS die Anzahl der auszugebenden Packungen angegeben werden (mindestens 1). 
-Dies gilt für Arzneimittel mit PZN und magistralen Zubereitungen, z.B. 2 Packungen (OP2), im Fall einer Magistralen Anwendung: Menge 1.</t>
+Dies gilt für Arzneimittel mit PZN und magistralen Zubereitungen.</t>
   </si>
   <si>
     <t>The amount that is to be dispensed for one fill.</t>
@@ -1462,7 +1456,7 @@
 </t>
   </si>
   <si>
-    <t>Dauer, für die die bereitgestellte Menge des Medikaments voraussichtlich ausreicht, z.B. 30 Tage. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Dauer, für die die bereitgestellte Menge des Medikaments voraussichtlich ausreicht. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
@@ -6561,10 +6555,10 @@
         <v>353</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>234</v>
+        <v>354</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6630,13 +6624,13 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6647,10 +6641,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6673,13 +6667,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6730,7 +6724,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6745,13 +6739,13 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6762,10 +6756,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6788,16 +6782,16 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6847,7 +6841,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6862,13 +6856,13 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6879,10 +6873,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6905,13 +6899,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6962,7 +6956,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6980,10 +6974,10 @@
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -6994,10 +6988,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7020,13 +7014,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7077,7 +7071,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7098,7 +7092,7 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7109,10 +7103,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7138,10 +7132,10 @@
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>157</v>
@@ -7194,7 +7188,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7215,7 +7209,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7226,14 +7220,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7255,10 +7249,10 @@
         <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>157</v>
@@ -7313,7 +7307,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7345,10 +7339,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7371,16 +7365,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7430,7 +7424,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7451,7 +7445,7 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7462,10 +7456,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7488,13 +7482,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7545,7 +7539,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7566,7 +7560,7 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7577,10 +7571,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7606,10 +7600,10 @@
         <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>157</v>
@@ -7662,7 +7656,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7683,7 +7677,7 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7694,14 +7688,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7723,10 +7717,10 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>157</v>
@@ -7781,7 +7775,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7813,10 +7807,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7839,13 +7833,13 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7896,7 +7890,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7917,7 +7911,7 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7928,10 +7922,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7954,13 +7948,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8011,7 +8005,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8032,7 +8026,7 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8043,10 +8037,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8069,13 +8063,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8126,7 +8120,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8147,7 +8141,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8158,10 +8152,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8184,19 +8178,19 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8245,7 +8239,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8263,10 +8257,10 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8277,10 +8271,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8303,16 +8297,16 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8362,7 +8356,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8380,24 +8374,24 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8420,13 +8414,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8477,7 +8471,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8495,24 +8489,24 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8535,16 +8529,16 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8594,7 +8588,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8612,10 +8606,10 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8626,10 +8620,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8652,13 +8646,13 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8709,7 +8703,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8730,7 +8724,7 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8741,10 +8735,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8770,10 +8764,10 @@
         <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>157</v>
@@ -8817,7 +8811,7 @@
         <v>138</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>21</v>
@@ -8826,7 +8820,7 @@
         <v>139</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8847,7 +8841,7 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8858,10 +8852,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8884,19 +8878,19 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8945,7 +8939,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8966,21 +8960,21 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9006,20 +9000,20 @@
         <v>110</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="R60" t="s" s="2">
         <v>21</v>
@@ -9043,10 +9037,10 @@
         <v>174</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9064,7 +9058,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9085,21 +9079,21 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9122,17 +9116,17 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9181,7 +9175,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9202,21 +9196,21 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9242,14 +9236,14 @@
         <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9298,7 +9292,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9307,7 +9301,7 @@
         <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>102</v>
@@ -9319,21 +9313,21 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9359,16 +9353,16 @@
         <v>110</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9417,7 +9411,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9438,21 +9432,21 @@
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9475,13 +9469,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9532,7 +9526,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9553,7 +9547,7 @@
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>305</v>
@@ -9564,10 +9558,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9590,13 +9584,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9647,7 +9641,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9665,10 +9659,10 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9679,10 +9673,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9705,13 +9699,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9762,7 +9756,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9783,7 +9777,7 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9794,10 +9788,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9823,10 +9817,10 @@
         <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>157</v>
@@ -9879,7 +9873,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9900,7 +9894,7 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9911,14 +9905,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9940,10 +9934,10 @@
         <v>135</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>157</v>
@@ -9998,7 +9992,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10030,10 +10024,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10056,16 +10050,16 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10094,10 +10088,10 @@
         <v>185</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -10115,7 +10109,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>90</v>
@@ -10133,24 +10127,24 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10176,10 +10170,10 @@
         <v>181</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10209,10 +10203,10 @@
         <v>185</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -10230,7 +10224,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10248,24 +10242,24 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10288,13 +10282,13 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10345,7 +10339,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10360,13 +10354,13 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
@@ -10377,14 +10371,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10403,16 +10397,16 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10462,7 +10456,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10483,7 +10477,7 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
@@ -10494,10 +10488,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10520,16 +10514,16 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10579,7 +10573,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10594,13 +10588,13 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:50:58+00:00</t>
+    <t>2026-03-20T15:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T15:30:14+00:00</t>
+    <t>2026-03-24T10:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T10:00:40+00:00</t>
+    <t>2026-03-24T15:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:12:36+00:00</t>
+    <t>2026-03-27T10:18:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:18:57+00:00</t>
+    <t>2026-03-30T07:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:39:16+00:00</t>
+    <t>2026-03-30T10:13:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T10:13:35+00:00</t>
+    <t>2026-04-01T13:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T13:59:59+00:00</t>
+    <t>2026-04-02T15:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -562,7 +562,7 @@
 * \"completed\": implizit mittels Custom Operation gesetzt, nachdem alle Abgaben durchgeführt wurden (Rezept komplett eingelöst) (TODO: techn. prüfen) 
 * \"entered-in-error\": nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde (TODO: techn. prüfen?) 
 * \"stopped\": TODO: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden)
-(nicht verwendet: on-hold, stopped, cancelled, draft, unknown)</t>
+(nicht verwendet: on-hold, cancelled, draft, unknown)</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:01:02+00:00</t>
+    <t>2026-04-07T09:06:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:06:22+00:00</t>
+    <t>2026-04-07T15:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T15:41:53+00:00</t>
+    <t>2026-04-07T16:09:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T16:09:01+00:00</t>
+    <t>2026-04-08T18:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T18:33:44+00:00</t>
+    <t>2026-04-09T06:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T06:40:16+00:00</t>
+    <t>2026-04-09T18:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T18:30:31+00:00</t>
+    <t>2026-04-10T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:48:51+00:00</t>
+    <t>2026-04-13T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:44:53+00:00</t>
+    <t>2026-04-13T15:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T15:27:52+00:00</t>
+    <t>2026-04-13T20:12:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T20:12:42+00:00</t>
+    <t>2026-04-14T10:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="537">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T10:13:14+00:00</t>
+    <t>2026-04-17T19:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -477,6 +477,10 @@
     <t>Zeitraum, über den die Medikation eingenommen werden soll. Wenn mehrere dosageInstruction-Zeilen vorhanden sind (z. B. bei einer ausschleichenden Dosierung), entspricht dieser Zeitraum dem frühesten Startdatum und dem spätesten Enddatum der dosageInstructions.</t>
   </si>
   <si>
+    <t>Element `MedicationRequest.effectiveDosePeriod` has a context of MedicationRequest based on following the parent source element upwards and mapping to `MedicationRequest`.
+Element `MedicationRequest.effectiveDosePeriod` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
@@ -494,7 +498,11 @@
     <t>Vollständige Darstellung der Dosierungsanweisungen</t>
   </si>
   <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>R5: `MedicationRequest.renderedDosageInstruction` (new:markdown)</t>
+  </si>
+  <si>
+    <t>Element `MedicationRequest.renderedDosageInstruction` has a context of MedicationRequest based on following the parent source element upwards and mapping to `MedicationRequest`.
+Element `MedicationRequest.renderedDosageInstruction` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
   </si>
   <si>
     <t>MedicationRequest.modifierExtension</t>
@@ -3189,7 +3197,9 @@
       <c r="M10" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
@@ -3247,7 +3257,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>141</v>
@@ -3259,7 +3269,7 @@
         <v>21</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>21</v>
@@ -3270,13 +3280,13 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>134</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>21</v>
@@ -3298,15 +3308,17 @@
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>21</v>
@@ -3364,7 +3376,7 @@
         <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>141</v>
@@ -3376,7 +3388,7 @@
         <v>21</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>21</v>
@@ -3387,14 +3399,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3416,16 +3428,16 @@
         <v>135</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>21</v>
@@ -3474,7 +3486,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3506,10 +3518,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3532,16 +3544,16 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3591,7 +3603,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3606,27 +3618,27 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3652,13 +3664,13 @@
         <v>110</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3684,11 +3696,11 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3706,7 +3718,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>90</v>
@@ -3721,16 +3733,16 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>21</v>
@@ -3738,10 +3750,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3764,16 +3776,16 @@
         <v>21</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3799,13 +3811,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3823,7 +3835,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3838,13 +3850,13 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>21</v>
@@ -3855,10 +3867,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3884,13 +3896,13 @@
         <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3901,7 +3913,7 @@
         <v>21</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>21</v>
@@ -3916,13 +3928,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3940,7 +3952,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>90</v>
@@ -3955,16 +3967,16 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>21</v>
@@ -3972,10 +3984,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3983,7 +3995,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>81</v>
@@ -3998,16 +4010,16 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4033,19 +4045,19 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
@@ -4055,7 +4067,7 @@
         <v>139</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4073,13 +4085,13 @@
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>21</v>
@@ -4087,13 +4099,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>21</v>
@@ -4115,16 +4127,16 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4135,7 +4147,7 @@
         <v>21</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>21</v>
@@ -4150,13 +4162,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -4174,7 +4186,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4192,13 +4204,13 @@
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>21</v>
@@ -4206,13 +4218,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>21</v>
@@ -4234,16 +4246,16 @@
         <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4269,11 +4281,11 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -4291,7 +4303,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4309,13 +4321,13 @@
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>21</v>
@@ -4323,10 +4335,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4352,10 +4364,10 @@
         <v>110</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4382,13 +4394,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -4406,7 +4418,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4421,16 +4433,16 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>21</v>
@@ -4438,10 +4450,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4464,16 +4476,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4523,7 +4535,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4544,7 +4556,7 @@
         <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>21</v>
@@ -4555,10 +4567,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4581,13 +4593,13 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4638,7 +4650,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4659,7 +4671,7 @@
         <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -4670,10 +4682,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4696,16 +4708,16 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4755,7 +4767,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>90</v>
@@ -4770,27 +4782,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4813,16 +4825,16 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4872,7 +4884,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>90</v>
@@ -4887,27 +4899,27 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4930,16 +4942,16 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4989,7 +5001,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5004,27 +5016,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5047,13 +5059,13 @@
         <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5104,7 +5116,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5119,16 +5131,16 @@
         <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>21</v>
@@ -5136,10 +5148,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5162,13 +5174,13 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5219,7 +5231,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5234,27 +5246,27 @@
         <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5277,13 +5289,13 @@
         <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5334,7 +5346,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5349,16 +5361,16 @@
         <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>21</v>
@@ -5366,10 +5378,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5392,13 +5404,13 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5449,7 +5461,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5464,16 +5476,16 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>21</v>
@@ -5481,10 +5493,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5507,16 +5519,16 @@
         <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5542,13 +5554,13 @@
         <v>21</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5566,7 +5578,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5581,13 +5593,13 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
@@ -5598,10 +5610,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5624,13 +5636,13 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5681,7 +5693,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5702,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>21</v>
@@ -5713,10 +5725,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5739,16 +5751,16 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5774,13 +5786,13 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5798,7 +5810,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5813,27 +5825,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5856,16 +5868,16 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5915,7 +5927,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5930,16 +5942,16 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
@@ -5947,10 +5959,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5973,13 +5985,13 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6030,7 +6042,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6045,13 +6057,13 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>21</v>
@@ -6062,10 +6074,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6091,10 +6103,10 @@
         <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6145,7 +6157,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6166,7 +6178,7 @@
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
@@ -6177,10 +6189,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6203,13 +6215,13 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6260,7 +6272,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6275,13 +6287,13 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>21</v>
@@ -6292,10 +6304,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6318,17 +6330,17 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6377,7 +6389,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6392,13 +6404,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>21</v>
@@ -6409,10 +6421,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6435,16 +6447,16 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6470,13 +6482,13 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6494,7 +6506,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6515,7 +6527,7 @@
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6526,10 +6538,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6552,13 +6564,13 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6609,7 +6621,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6624,13 +6636,13 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6641,10 +6653,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6667,13 +6679,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6724,7 +6736,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6739,13 +6751,13 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6756,10 +6768,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6782,16 +6794,16 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6841,7 +6853,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6856,13 +6868,13 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6873,10 +6885,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6899,13 +6911,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6956,7 +6968,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6974,10 +6986,10 @@
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -6988,10 +7000,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7014,13 +7026,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7071,7 +7083,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7092,7 +7104,7 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7103,14 +7115,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7132,13 +7144,13 @@
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7188,7 +7200,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7209,7 +7221,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7220,14 +7232,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7249,16 +7261,16 @@
         <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -7307,7 +7319,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7339,10 +7351,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7365,16 +7377,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7424,7 +7436,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7445,7 +7457,7 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7456,10 +7468,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7482,13 +7494,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7539,7 +7551,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7560,7 +7572,7 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7571,14 +7583,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7600,13 +7612,13 @@
         <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7656,7 +7668,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7677,7 +7689,7 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7688,14 +7700,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7717,16 +7729,16 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7775,7 +7787,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7807,10 +7819,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7833,13 +7845,13 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7890,7 +7902,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7911,7 +7923,7 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7922,10 +7934,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7948,13 +7960,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8005,7 +8017,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8026,7 +8038,7 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8037,10 +8049,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8063,13 +8075,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8120,7 +8132,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8141,7 +8153,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8152,10 +8164,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8178,19 +8190,19 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8239,7 +8251,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8257,10 +8269,10 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8271,10 +8283,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8297,16 +8309,16 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8356,7 +8368,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8374,24 +8386,24 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8414,13 +8426,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8471,7 +8483,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8489,24 +8501,24 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8529,16 +8541,16 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8588,7 +8600,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8606,10 +8618,10 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8620,10 +8632,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8646,13 +8658,13 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8703,7 +8715,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8724,7 +8736,7 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8735,14 +8747,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8764,13 +8776,13 @@
         <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8811,7 +8823,7 @@
         <v>138</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>21</v>
@@ -8820,7 +8832,7 @@
         <v>139</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8841,7 +8853,7 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8852,10 +8864,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8878,19 +8890,19 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8939,7 +8951,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8960,21 +8972,21 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9000,20 +9012,20 @@
         <v>110</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q60" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="R60" t="s" s="2">
         <v>21</v>
@@ -9034,13 +9046,13 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9058,7 +9070,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9079,21 +9091,21 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9116,17 +9128,17 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9175,7 +9187,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9196,21 +9208,21 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9236,14 +9248,14 @@
         <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9292,7 +9304,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9301,7 +9313,7 @@
         <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>102</v>
@@ -9313,21 +9325,21 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9353,16 +9365,16 @@
         <v>110</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9411,7 +9423,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9432,21 +9444,21 @@
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9469,13 +9481,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9526,7 +9538,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9547,10 +9559,10 @@
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>21</v>
@@ -9558,10 +9570,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9584,13 +9596,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9641,7 +9653,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9659,10 +9671,10 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9673,10 +9685,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9699,13 +9711,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9756,7 +9768,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9777,7 +9789,7 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9788,14 +9800,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9817,13 +9829,13 @@
         <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9873,7 +9885,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9894,7 +9906,7 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9905,14 +9917,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9934,16 +9946,16 @@
         <v>135</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>21</v>
@@ -9992,7 +10004,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10024,10 +10036,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10050,16 +10062,16 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10085,13 +10097,13 @@
         <v>21</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -10109,7 +10121,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>90</v>
@@ -10127,24 +10139,24 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10167,13 +10179,13 @@
         <v>21</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10200,13 +10212,13 @@
         <v>21</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -10224,7 +10236,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10242,24 +10254,24 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10282,13 +10294,13 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10339,7 +10351,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10354,13 +10366,13 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
@@ -10371,14 +10383,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10397,16 +10409,16 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10456,7 +10468,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10477,7 +10489,7 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
@@ -10488,10 +10500,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10514,16 +10526,16 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10573,7 +10585,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10588,13 +10600,13 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T19:15:07+00:00</t>
+    <t>2026-04-20T08:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T08:20:06+00:00</t>
+    <t>2026-04-20T16:24:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="538">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T16:24:35+00:00</t>
+    <t>2026-04-20T19:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -535,7 +535,7 @@
 </t>
   </si>
   <si>
-    <t>Gepante-Abgabe-ID. TODO: Verwendung noch zu prüfen, evtl. basedon mit logischem Identifier ausreichend.</t>
+    <t>Gepante-Abgabe-ID.</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -562,15 +562,10 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status der geplanten Abgabe: active | completed | entered-in-error | stopped. Details siehe Definition.</t>
-  </si>
-  <si>
-    <t>Status der geplanten Abgabe:
-* \"active\": offene, geplante Abgabe 
-* \"completed\": implizit mittels Custom Operation gesetzt, nachdem alle Abgaben durchgeführt wurden (Rezept komplett eingelöst) (TODO: techn. prüfen) 
-* \"entered-in-error\": nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde (TODO: techn. prüfen?) 
-* \"stopped\": TODO: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden)
-(nicht verwendet: on-hold, cancelled, draft, unknown)</t>
+    <t>Status der geplanten Abgabe. Mögliche Ausprägung: [active | completed | entered-in-error | stopped]. Bedeutung: active: offene, geplante Abgabe | completed: geplante Abgabe abgeschlossen | entered-in-error: nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde | stopped: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden)</t>
+  </si>
+  <si>
+    <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
@@ -601,7 +596,7 @@
 </t>
   </si>
   <si>
-    <t>Grund für den aktuellen Status: https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Grund des aktuellen Status: https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the MedicationRequest.</t>
@@ -628,8 +623,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>Die Geplante Abgabe stellt eine Anforderung und Ermächtigung 
-zum Handeln durch den Antragsteller dar, daher ist intent immer "order".</t>
+    <t>Die geplante Abgabe stellt einen Auftrag zur Durchführung und eine Autorisierung des Verfassers dar; daher ist intent immer "order".</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -940,8 +934,7 @@
   </si>
   <si>
     <t>Der Arzt oder die Ärztin, die die geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist 
-(eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen).
-TODO: HL7ATCore-Practitioner-Profile profilieren.</t>
+(eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen).</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -960,6 +953,9 @@
 </t>
   </si>
   <si>
+    <t>Durchführende Person. Keine Verwendung in der geplanten Abgabe.</t>
+  </si>
+  <si>
     <t>The specified desired performer of the medication treatment (e.g. the performer of the medication administration).</t>
   </si>
   <si>
@@ -1000,7 +996,7 @@
 </t>
   </si>
   <si>
-    <t>Person der Dateineingabe. Gemäß Vorgaben im CDA keine Verwendung in der geplanten Abgabe. TODO: Abstimmung der Verwendung mit e-Diagnose.</t>
+    <t>Person der Dateineingabe. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The person who entered the order on behalf of another individual for example in the case of a verbal or a telephone order.</t>
@@ -1015,7 +1011,7 @@
     <t>MedicationRequest.reasonCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Grund für die Verordnung des Arzneimittels als Code oder Referenz. Bis zur Verfügbarkeit von e-Diagnose keine Verwendung in geplanter Abgabe. </t>
+    <t>Grund für die Verordnung des Arzneimittels als Code oder Referenz. Bis zur Verfügbarkeit von e-Diagnose keine Verwendung in geplanter Abgabe.</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -1074,7 +1070,7 @@
 </t>
   </si>
   <si>
-    <t>URL, die auf ein Protokoll (Richtlinie, Guideline) verweist, das von dieser 
+    <t>URL, die auf eine Richtlinie/Guideline verweist, die von dieser 
 geplanten Abgabe ganz oder teilweise eingehalten wird. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
@@ -1090,7 +1086,7 @@
     <t>MedicationRequest.instantiatesUri</t>
   </si>
   <si>
-    <t>URL, die auf ein extern gepflegtes Protokoll (Richtlinie, Guideline) verweist, das von dieser 
+    <t>URL, die auf eine externe gepflegte Richtlinie/Guideline verweist, die von dieser 
 geplanten Abgabe ganz oder teilweise eingehalten wird. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
@@ -1104,9 +1100,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf die (aktuelle) Version des zugrundeliegenden Medikationsplaneintrags, auf dem diese geplante Abgabe basiert.
-TODO: zu prüfen: zusätzliche logische Referenz: reference.identifier 
-{Medikationsplaneintrag-ID}_{Medikationsplaneintrag-ID_Version}.</t>
+    <t>Referenz auf die (aktuelle) Version des zugrundeliegenden Medikationsplaneintrags, auf dem diese geplante Abgabe basiert.</t>
   </si>
   <si>
     <t>A plan or request that is fulfilled in whole or in part by this medication request.</t>
@@ -1122,9 +1116,8 @@
   </si>
   <si>
     <t>Als groupIdentifier dient die eMED-ID, die auch im e-Rezept mitgeführt wird. 
-Werden von einem:r Arzt:Ärtztin mehrere Arzneimittel gleichzeitig verordnet, 
-wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').
-TODO: eMED-ID Wording ist evtl. aufgrund des Parallelbetriebs noch anzupassen</t>
+Werden von einem:r Arzt:Ärtztin mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine 
+geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
   </si>
   <si>
     <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition or prescription.</t>
@@ -1186,8 +1179,7 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen zur geplanten Abgabe (Kommunikations zw. Arzt und Apotheke); die nicht die Dosierung betreffen. 
-TODO: prüfen was CDA derzeit zulässt; HL7 Consultation, ob Feld benötigt</t>
+    <t>Zusätzliche Informationen zur geplanten Abgabe (Kommunikation zwischen Arzt und Apotheke, die nicht die Dosierung betreffen).</t>
   </si>
   <si>
     <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
@@ -1209,7 +1201,7 @@
 </t>
   </si>
   <si>
-    <t>Angabe der Dosierinformationen. TODO: Dosiervarianten.</t>
+    <t>Angabe der Dosierinformationen.</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -1363,14 +1355,13 @@
 </t>
   </si>
   <si>
-    <t>Die Anzahl der weiteren möglichen Einlösungen ist abhängig von der Rezeptart (siehe Definition).</t>
-  </si>
-  <si>
-    <t>Anzahl der weiteren möglichen Einlösungen:
+    <t>Die Anzahl der weiteren möglichen Einlösungen ist abhängig von der Rezeptart: Kassenrezept: keine weitere Einlösung möglich (fixer Wert 0). Privatrezept: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden. Sustitutionsrezept: keine weitere Einlösung möglich (fixer Wert 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anzahl der weiteren möglichen Einlösungen:
 * **Kassenrezept**: keine weitere Einlösung möglich (fixer Wert 0)
 * **Privatrezept**: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden
-* **Sustitutionsrzepet**: keine weitere Einlösung möglich (fixer Wert 0) 
-TODO: Techn. Prüfung: Wenn Kassenrezept oder Substitutionsrezept, dann 0. Verpflichtende Eingabe, wenn Privatrezept, max 6.</t>
+* **Sustitutionsrezept**: keine weitere Einlösung möglich (fixer Wert 0) </t>
   </si>
   <si>
     <t>It reflects the prescribers' perspective for the validity of the prescription. Dispenses must not be made against the prescription outside of this period. The lower-bound of the Dispensing Window signifies the earliest date that the prescription can be filled for the first time. If an upper-bound is not specified then the Prescription is open-ended or will default to a stale-date based on regulations.</t>
@@ -1413,7 +1404,7 @@
     <t>MedicationRequest.dispenseRequest.quantity</t>
   </si>
   <si>
-    <t>Menge des Medikaments, die bei jeder Abgabe bereitgestellt werden soll. 
+    <t>Menge des Medikaments, die bei jeder Abgabe bereitgestellt werden soll.
 Da sich die Angaben zum Arzneimittel jeweils auf eine Packung der Arznei beziehen, MUSS die Anzahl der auszugebenden Packungen angegeben werden (mindestens 1). 
 Dies gilt für Arzneimittel mit PZN und magistralen Zubereitungen.</t>
   </si>
@@ -5407,10 +5398,10 @@
         <v>290</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>236</v>
+        <v>291</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5476,16 +5467,16 @@
         <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>21</v>
@@ -5493,10 +5484,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5525,10 +5516,10 @@
         <v>236</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5557,10 +5548,10 @@
         <v>187</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>21</v>
@@ -5578,7 +5569,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5593,13 +5584,13 @@
         <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>21</v>
@@ -5610,10 +5601,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5636,13 +5627,13 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5693,7 +5684,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5714,10 +5705,10 @@
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>21</v>
@@ -5725,10 +5716,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5754,13 +5745,13 @@
         <v>183</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5789,10 +5780,10 @@
         <v>187</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5810,7 +5801,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5825,27 +5816,27 @@
         <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5868,16 +5859,16 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5927,7 +5918,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5942,16 +5933,16 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>179</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>21</v>
@@ -5959,10 +5950,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5985,13 +5976,13 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6042,7 +6033,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6057,13 +6048,13 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>21</v>
@@ -6074,10 +6065,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6103,10 +6094,10 @@
         <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6157,7 +6148,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6178,7 +6169,7 @@
         <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>21</v>
@@ -6189,10 +6180,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6215,13 +6206,13 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6272,7 +6263,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6287,13 +6278,13 @@
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>21</v>
@@ -6304,10 +6295,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6333,14 +6324,14 @@
         <v>163</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -6389,7 +6380,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6404,13 +6395,13 @@
         <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>21</v>
@@ -6421,10 +6412,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6450,13 +6441,13 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6485,10 +6476,10 @@
         <v>187</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -6506,7 +6497,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6527,7 +6518,7 @@
         <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>21</v>
@@ -6538,10 +6529,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6564,13 +6555,13 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6621,7 +6612,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6636,13 +6627,13 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>21</v>
@@ -6653,10 +6644,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6679,13 +6670,13 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6736,7 +6727,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6751,13 +6742,13 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>21</v>
@@ -6768,10 +6759,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6794,16 +6785,16 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6853,7 +6844,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6868,13 +6859,13 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>21</v>
@@ -6885,10 +6876,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6911,13 +6902,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6968,7 +6959,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6986,10 +6977,10 @@
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>21</v>
@@ -7000,10 +6991,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7026,13 +7017,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7083,7 +7074,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7104,7 +7095,7 @@
         <v>21</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>21</v>
@@ -7115,10 +7106,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7144,10 +7135,10 @@
         <v>135</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>159</v>
@@ -7200,7 +7191,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7221,7 +7212,7 @@
         <v>21</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>21</v>
@@ -7232,14 +7223,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7261,10 +7252,10 @@
         <v>135</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>159</v>
@@ -7319,7 +7310,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7351,10 +7342,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7377,16 +7368,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7436,7 +7427,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7457,7 +7448,7 @@
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>21</v>
@@ -7468,10 +7459,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7494,13 +7485,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7551,7 +7542,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7572,7 +7563,7 @@
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7583,10 +7574,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7612,10 +7603,10 @@
         <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>159</v>
@@ -7668,7 +7659,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7689,7 +7680,7 @@
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7700,14 +7691,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7729,10 +7720,10 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>159</v>
@@ -7787,7 +7778,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7819,10 +7810,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7845,13 +7836,13 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7902,7 +7893,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7923,7 +7914,7 @@
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7934,10 +7925,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7960,13 +7951,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8017,7 +8008,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8038,7 +8029,7 @@
         <v>21</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -8049,10 +8040,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8075,13 +8066,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8132,7 +8123,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8153,7 +8144,7 @@
         <v>21</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>21</v>
@@ -8164,10 +8155,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8190,19 +8181,19 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -8251,7 +8242,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8269,10 +8260,10 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8283,10 +8274,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8309,16 +8300,16 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8368,7 +8359,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8386,24 +8377,24 @@
         <v>21</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8426,13 +8417,13 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8483,7 +8474,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8501,24 +8492,24 @@
         <v>21</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8541,16 +8532,16 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8600,7 +8591,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8618,10 +8609,10 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8632,10 +8623,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8658,13 +8649,13 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8715,7 +8706,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8736,7 +8727,7 @@
         <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8747,10 +8738,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8776,10 +8767,10 @@
         <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>159</v>
@@ -8823,7 +8814,7 @@
         <v>138</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>21</v>
@@ -8832,7 +8823,7 @@
         <v>139</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8853,7 +8844,7 @@
         <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
@@ -8864,10 +8855,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8890,19 +8881,19 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>21</v>
@@ -8951,7 +8942,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8972,21 +8963,21 @@
         <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9012,20 +9003,20 @@
         <v>110</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R60" t="s" s="2">
         <v>21</v>
@@ -9049,10 +9040,10 @@
         <v>176</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -9070,7 +9061,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9091,21 +9082,21 @@
         <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9128,17 +9119,17 @@
         <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9187,7 +9178,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9208,21 +9199,21 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9248,14 +9239,14 @@
         <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
@@ -9304,7 +9295,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9313,7 +9304,7 @@
         <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>102</v>
@@ -9325,21 +9316,21 @@
         <v>21</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9365,16 +9356,16 @@
         <v>110</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9423,7 +9414,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9444,21 +9435,21 @@
         <v>21</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9481,13 +9472,13 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9538,7 +9529,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9559,10 +9550,10 @@
         <v>21</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>21</v>
@@ -9570,10 +9561,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9596,13 +9587,13 @@
         <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9653,7 +9644,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9671,10 +9662,10 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9685,10 +9676,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9711,13 +9702,13 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9768,7 +9759,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9789,7 +9780,7 @@
         <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>21</v>
@@ -9800,10 +9791,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9829,10 +9820,10 @@
         <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>159</v>
@@ -9885,7 +9876,7 @@
         <v>21</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9906,7 +9897,7 @@
         <v>21</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>21</v>
@@ -9917,14 +9908,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9946,10 +9937,10 @@
         <v>135</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>159</v>
@@ -10004,7 +9995,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10036,10 +10027,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10062,16 +10053,16 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10100,10 +10091,10 @@
         <v>187</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>21</v>
@@ -10121,7 +10112,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>90</v>
@@ -10139,24 +10130,24 @@
         <v>21</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10182,10 +10173,10 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10215,10 +10206,10 @@
         <v>187</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>21</v>
@@ -10236,7 +10227,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10254,24 +10245,24 @@
         <v>21</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10294,13 +10285,13 @@
         <v>21</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10351,7 +10342,7 @@
         <v>21</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10366,13 +10357,13 @@
         <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>21</v>
@@ -10383,14 +10374,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10409,16 +10400,16 @@
         <v>21</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10468,7 +10459,7 @@
         <v>21</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10489,7 +10480,7 @@
         <v>21</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>21</v>
@@ -10500,10 +10491,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10526,16 +10517,16 @@
         <v>21</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10585,7 +10576,7 @@
         <v>21</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10600,13 +10591,13 @@
         <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T19:04:12+00:00</t>
+    <t>2026-04-21T08:44:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T08:44:51+00:00</t>
+    <t>2026-04-21T11:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:54:48+00:00</t>
+    <t>2026-04-21T14:09:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:09:10+00:00</t>
+    <t>2026-04-21T17:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:01:26+00:00</t>
+    <t>2026-04-22T08:49:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T08:49:17+00:00</t>
+    <t>2026-04-22T10:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:01:54+00:00</t>
+    <t>2026-04-22T10:11:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:11:27+00:00</t>
+    <t>2026-04-28T11:58:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-28T11:58:02+00:00</t>
+    <t>2026-04-29T14:27:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T14:27:58+00:00</t>
+    <t>2026-04-30T15:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:16:21+00:00</t>
+    <t>2026-04-30T15:23:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:23:35+00:00</t>
+    <t>2026-05-04T14:46:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-mr-geplante-abgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:46:25+00:00</t>
+    <t>2026-05-08T13:20:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -535,7 +535,7 @@
 </t>
   </si>
   <si>
-    <t>Gepante-Abgabe-ID.</t>
+    <t>Logischer Identifier. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -1589,8 +1589,7 @@
     <t>MedicationRequest.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht.
-Erläutert die Absicht des verschreibenden Arztes. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Gibt an, ob das Arzneimittel substituiert werden darf (Absicht des Arztes, der die geplante Abgabe erstellt). Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
